--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -62871,7 +62871,7 @@
         <v>31342</v>
       </c>
       <c r="C2718" t="n">
-        <v>66.4000015258789</v>
+        <v>66.5</v>
       </c>
       <c r="D2718" t="n">
         <v>64.0999984741211</v>
@@ -62883,6 +62883,29 @@
         <v>66.5</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>71487</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>66.9000015258789</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>60.0999984741211</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>66.9000015258789</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>60.7999992370605</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>33511</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>61.5999984741211</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>59.2000007629395</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>61.2999992370605</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>61.5999984741211</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>42935</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>64.4000015258789</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>61</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>61.9000015258789</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>62.4000015258789</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>16506</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>64.1999969482422</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>62</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>62.7000007629395</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>62.7000007629395</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>51297</v>
+        <v>46778</v>
       </c>
       <c r="C2715" t="n">
-        <v>65.6999969482422</v>
+        <v>64.5</v>
       </c>
       <c r="D2715" t="n">
-        <v>63.2000007629395</v>
+        <v>61.9000015258789</v>
       </c>
       <c r="E2715" t="n">
-        <v>65</v>
+        <v>62.5</v>
       </c>
       <c r="F2715" t="n">
-        <v>63.7000007629395</v>
+        <v>64.5</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>32290</v>
+        <v>51297</v>
       </c>
       <c r="C2716" t="n">
-        <v>64.5</v>
+        <v>65.6999969482422</v>
       </c>
       <c r="D2716" t="n">
-        <v>62.7000007629395</v>
+        <v>63.2000007629395</v>
       </c>
       <c r="E2716" t="n">
-        <v>64.5</v>
+        <v>65</v>
       </c>
       <c r="F2716" t="n">
-        <v>62.9000015258789</v>
+        <v>63.7000007629395</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>55566</v>
+        <v>32290</v>
       </c>
       <c r="C2717" t="n">
-        <v>65.5999984741211</v>
+        <v>64.5</v>
       </c>
       <c r="D2717" t="n">
-        <v>63.2999992370605</v>
+        <v>62.7000007629395</v>
       </c>
       <c r="E2717" t="n">
-        <v>63.7000007629395</v>
+        <v>64.5</v>
       </c>
       <c r="F2717" t="n">
-        <v>64.3000030517578</v>
+        <v>62.9000015258789</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>31342</v>
+        <v>55566</v>
       </c>
       <c r="C2718" t="n">
-        <v>66.5</v>
+        <v>65.5999984741211</v>
       </c>
       <c r="D2718" t="n">
-        <v>64.0999984741211</v>
+        <v>63.2999992370605</v>
       </c>
       <c r="E2718" t="n">
+        <v>63.7000007629395</v>
+      </c>
+      <c r="F2718" t="n">
         <v>64.3000030517578</v>
-      </c>
-      <c r="F2718" t="n">
-        <v>66.5</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>71487</v>
+        <v>31342</v>
       </c>
       <c r="C2719" t="n">
-        <v>66.9000015258789</v>
+        <v>66.5</v>
       </c>
       <c r="D2719" t="n">
-        <v>60.0999984741211</v>
+        <v>64.0999984741211</v>
       </c>
       <c r="E2719" t="n">
-        <v>66.9000015258789</v>
+        <v>64.3000030517578</v>
       </c>
       <c r="F2719" t="n">
-        <v>60.7999992370605</v>
+        <v>66.5</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>33511</v>
+        <v>71487</v>
       </c>
       <c r="C2720" t="n">
-        <v>61.5999984741211</v>
+        <v>66.9000015258789</v>
       </c>
       <c r="D2720" t="n">
-        <v>59.2000007629395</v>
+        <v>60.0999984741211</v>
       </c>
       <c r="E2720" t="n">
-        <v>61.2999992370605</v>
+        <v>66.9000015258789</v>
       </c>
       <c r="F2720" t="n">
-        <v>61.5999984741211</v>
+        <v>60.7999992370605</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>42935</v>
+        <v>33511</v>
       </c>
       <c r="C2721" t="n">
-        <v>64.4000015258789</v>
+        <v>61.5999984741211</v>
       </c>
       <c r="D2721" t="n">
-        <v>61</v>
+        <v>59.2000007629395</v>
       </c>
       <c r="E2721" t="n">
-        <v>61.9000015258789</v>
+        <v>61.2999992370605</v>
       </c>
       <c r="F2721" t="n">
-        <v>62.4000015258789</v>
+        <v>61.5999984741211</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>16506</v>
+        <v>42935</v>
       </c>
       <c r="C2722" t="n">
-        <v>64.1999969482422</v>
+        <v>64.4000015258789</v>
       </c>
       <c r="D2722" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2722" t="n">
-        <v>62.7000007629395</v>
+        <v>61.9000015258789</v>
       </c>
       <c r="F2722" t="n">
-        <v>62.7000007629395</v>
+        <v>62.4000015258789</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>65</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>64.0999984741211</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>8.24608993530273</v>
+        <v>8.24609184265137</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>9.75</v>
       </c>
       <c r="G12" t="n">
-        <v>8.02388954162598</v>
+        <v>8.02389144897461</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>9.875</v>
       </c>
       <c r="G13" t="n">
-        <v>8.1267614364624</v>
+        <v>8.12675952911377</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G14" t="n">
-        <v>8.0074291229248</v>
+        <v>8.00743007659912</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G15" t="n">
-        <v>8.0814962387085</v>
+        <v>8.08149814605713</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G17" t="n">
-        <v>7.97039794921875</v>
+        <v>7.97039842605591</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>8.01566028594971</v>
+        <v>8.01566219329834</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G19" t="n">
-        <v>7.99920129776001</v>
+        <v>7.99920225143433</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G20" t="n">
-        <v>7.90044593811035</v>
+        <v>7.90044498443604</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G22" t="n">
-        <v>7.92924928665161</v>
+        <v>7.92925024032593</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>7.8510684967041</v>
+        <v>7.85106897354126</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>7.8510684967041</v>
+        <v>7.85106897354126</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>7.84695243835449</v>
+        <v>7.84695196151733</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.5</v>
       </c>
       <c r="G27" t="n">
-        <v>7.81814956665039</v>
+        <v>7.81814908981323</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.5</v>
       </c>
       <c r="G28" t="n">
-        <v>7.81814956665039</v>
+        <v>7.81814908981323</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.5</v>
       </c>
       <c r="G29" t="n">
-        <v>7.81814956665039</v>
+        <v>7.81814908981323</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G30" t="n">
-        <v>7.8099193572998</v>
+        <v>7.80991888046265</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G31" t="n">
-        <v>7.8099193572998</v>
+        <v>7.80991888046265</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.5</v>
       </c>
       <c r="G32" t="n">
-        <v>7.81814956665039</v>
+        <v>7.81814908981323</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.5</v>
       </c>
       <c r="G33" t="n">
-        <v>7.81814956665039</v>
+        <v>7.81814908981323</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.5</v>
       </c>
       <c r="G34" t="n">
-        <v>7.81814956665039</v>
+        <v>7.81814908981323</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.5</v>
       </c>
       <c r="G35" t="n">
-        <v>7.81814956665039</v>
+        <v>7.81814908981323</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.5</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81814956665039</v>
+        <v>7.81814908981323</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.5</v>
       </c>
       <c r="G37" t="n">
-        <v>7.81814956665039</v>
+        <v>7.81814908981323</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>7.8099193572998</v>
+        <v>7.80991888046265</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>7.78523111343384</v>
+        <v>7.78523063659668</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G40" t="n">
-        <v>7.5836033821106</v>
+        <v>7.58360576629639</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G42" t="n">
-        <v>7.63709735870361</v>
+        <v>7.63709926605225</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G43" t="n">
-        <v>7.62475442886353</v>
+        <v>7.62475395202637</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.55480098724365</v>
+        <v>7.55480194091797</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G45" t="n">
-        <v>7.49307918548584</v>
+        <v>7.49307823181152</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.48896503448486</v>
+        <v>7.48896551132202</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G47" t="n">
-        <v>7.48896503448486</v>
+        <v>7.48896551132202</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>7.78523111343384</v>
+        <v>7.78523063659668</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>7.78523111343384</v>
+        <v>7.78523063659668</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>7.78523111343384</v>
+        <v>7.78523063659668</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>7.78523111343384</v>
+        <v>7.78523063659668</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>7.78523111343384</v>
+        <v>7.78523063659668</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G56" t="n">
-        <v>7.8675274848938</v>
+        <v>7.86752796173096</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G58" t="n">
-        <v>8.03212070465088</v>
+        <v>8.03211975097656</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G59" t="n">
-        <v>8.0074291229248</v>
+        <v>8.00743007659912</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99920129776001</v>
+        <v>7.99920225143433</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.75</v>
       </c>
       <c r="G61" t="n">
-        <v>8.02388954162598</v>
+        <v>8.02389144897461</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G62" t="n">
-        <v>7.98274040222168</v>
+        <v>7.98274230957031</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G63" t="n">
-        <v>8.11441421508789</v>
+        <v>8.11441612243652</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.75</v>
       </c>
       <c r="G65" t="n">
-        <v>8.02388954162598</v>
+        <v>8.02389144897461</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G66" t="n">
-        <v>8.11441421508789</v>
+        <v>8.11441612243652</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>7.98274040222168</v>
+        <v>7.98274230957031</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>7.98274040222168</v>
+        <v>7.98274230957031</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>7.98274040222168</v>
+        <v>7.98274230957031</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G70" t="n">
-        <v>7.93336486816406</v>
+        <v>7.93336582183838</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G71" t="n">
-        <v>7.89221429824829</v>
+        <v>7.8922176361084</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.75</v>
       </c>
       <c r="G72" t="n">
-        <v>8.02388954162598</v>
+        <v>8.02389144897461</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.75</v>
       </c>
       <c r="G73" t="n">
-        <v>8.02388954162598</v>
+        <v>8.02389144897461</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.75</v>
       </c>
       <c r="G74" t="n">
-        <v>8.02388954162598</v>
+        <v>8.02389144897461</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G76" t="n">
-        <v>8.03212070465088</v>
+        <v>8.03211975097656</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G77" t="n">
-        <v>8.1473331451416</v>
+        <v>8.14733505249023</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="G78" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="G79" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="G81" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10</v>
       </c>
       <c r="G82" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25432014465332</v>
+        <v>8.254319190979</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10</v>
       </c>
       <c r="G84" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G85" t="n">
-        <v>8.22140026092529</v>
+        <v>8.22140121459961</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>10</v>
       </c>
       <c r="G86" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>10</v>
       </c>
       <c r="G87" t="n">
-        <v>8.22963237762451</v>
+        <v>8.22963047027588</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>8.0897274017334</v>
+        <v>8.08972835540771</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>8.29133987426758</v>
+        <v>8.29134082794189</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G93" t="n">
-        <v>8.08132839202881</v>
+        <v>8.08132648468018</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>8.06452560424805</v>
+        <v>8.06452465057373</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>8.04772567749023</v>
+        <v>8.04772281646729</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G100" t="n">
-        <v>8.14852905273438</v>
+        <v>8.14853096008301</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>8.14852905273438</v>
+        <v>8.14853096008301</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>8.1401309967041</v>
+        <v>8.14013004302979</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G104" t="n">
-        <v>8.13173007965088</v>
+        <v>8.13172912597656</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G105" t="n">
-        <v>8.13173007965088</v>
+        <v>8.13172912597656</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.75</v>
       </c>
       <c r="G106" t="n">
-        <v>8.19053363800049</v>
+        <v>8.1905345916748</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.75</v>
       </c>
       <c r="G107" t="n">
-        <v>8.19053363800049</v>
+        <v>8.1905345916748</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.75</v>
       </c>
       <c r="G108" t="n">
-        <v>8.19053363800049</v>
+        <v>8.1905345916748</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.75</v>
       </c>
       <c r="G109" t="n">
-        <v>8.19053363800049</v>
+        <v>8.1905345916748</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.75</v>
       </c>
       <c r="G110" t="n">
-        <v>8.19053363800049</v>
+        <v>8.1905345916748</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.75</v>
       </c>
       <c r="G111" t="n">
-        <v>8.19053363800049</v>
+        <v>8.1905345916748</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.75</v>
       </c>
       <c r="G112" t="n">
-        <v>8.19053363800049</v>
+        <v>8.1905345916748</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.75</v>
       </c>
       <c r="G113" t="n">
-        <v>8.19053363800049</v>
+        <v>8.1905345916748</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.75</v>
       </c>
       <c r="G114" t="n">
-        <v>8.19053363800049</v>
+        <v>8.1905345916748</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G115" t="n">
-        <v>8.06452560424805</v>
+        <v>8.06452465057373</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G116" t="n">
-        <v>8.06452560424805</v>
+        <v>8.06452465057373</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G117" t="n">
-        <v>8.06452560424805</v>
+        <v>8.06452465057373</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>8.02252578735352</v>
+        <v>8.02252197265625</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.02252578735352</v>
+        <v>8.02252197265625</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>8.0393238067627</v>
+        <v>8.03932285308838</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.5</v>
       </c>
       <c r="G121" t="n">
-        <v>7.98051977157593</v>
+        <v>7.98052024841309</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>8.02252578735352</v>
+        <v>8.02252197265625</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G125" t="n">
-        <v>7.89651441574097</v>
+        <v>7.89651489257812</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G127" t="n">
-        <v>7.81250953674316</v>
+        <v>7.81251001358032</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.25</v>
       </c>
       <c r="G128" t="n">
-        <v>7.77050590515137</v>
+        <v>7.77050638198853</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.25</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77050590515137</v>
+        <v>7.77050638198853</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>7.81250953674316</v>
+        <v>7.81251001358032</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.5</v>
       </c>
       <c r="G134" t="n">
-        <v>7.98051977157593</v>
+        <v>7.98052024841309</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G135" t="n">
-        <v>8.06452560424805</v>
+        <v>8.06452465057373</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.05612373352051</v>
+        <v>8.05612468719482</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G137" t="n">
-        <v>8.05612373352051</v>
+        <v>8.05612468719482</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.05612373352051</v>
+        <v>8.05612468719482</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>8.05612373352051</v>
+        <v>8.05612468719482</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.05612373352051</v>
+        <v>8.05612468719482</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>8.05612373352051</v>
+        <v>8.05612468719482</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>8.05612373352051</v>
+        <v>8.05612468719482</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G143" t="n">
-        <v>8.05612373352051</v>
+        <v>8.05612468719482</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G145" t="n">
-        <v>7.89651441574097</v>
+        <v>7.89651489257812</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>7.867112159729</v>
+        <v>7.86711168289185</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>7.81250953674316</v>
+        <v>7.81251001358032</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>7.81250953674316</v>
+        <v>7.81251001358032</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G149" t="n">
-        <v>7.68649816513062</v>
+        <v>7.68650102615356</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G150" t="n">
-        <v>7.68649816513062</v>
+        <v>7.68650102615356</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.64449882507324</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G152" t="n">
-        <v>7.64449882507324</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G153" t="n">
-        <v>7.64449882507324</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G154" t="n">
-        <v>7.64449882507324</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G155" t="n">
-        <v>7.64449882507324</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G157" t="n">
-        <v>7.64449882507324</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>9.25</v>
       </c>
       <c r="G158" t="n">
-        <v>7.77050590515137</v>
+        <v>7.77050638198853</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.25</v>
       </c>
       <c r="G159" t="n">
-        <v>7.77050590515137</v>
+        <v>7.77050638198853</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.25</v>
       </c>
       <c r="G160" t="n">
-        <v>7.77050590515137</v>
+        <v>7.77050638198853</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.25</v>
       </c>
       <c r="G161" t="n">
-        <v>7.77050590515137</v>
+        <v>7.77050638198853</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.25</v>
       </c>
       <c r="G162" t="n">
-        <v>7.77050590515137</v>
+        <v>7.77050638198853</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.25</v>
       </c>
       <c r="G163" t="n">
-        <v>7.77050590515137</v>
+        <v>7.77050638198853</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G166" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G167" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G168" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G172" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G174" t="n">
-        <v>7.87131261825562</v>
+        <v>7.87131309509277</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G175" t="n">
-        <v>7.74530410766602</v>
+        <v>7.74530458450317</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G176" t="n">
-        <v>7.74530410766602</v>
+        <v>7.74530458450317</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G177" t="n">
-        <v>7.74530410766602</v>
+        <v>7.74530458450317</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G178" t="n">
-        <v>7.74530410766602</v>
+        <v>7.74530458450317</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G179" t="n">
-        <v>7.74530410766602</v>
+        <v>7.74530458450317</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>7.72850322723389</v>
+        <v>7.7285041809082</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9</v>
       </c>
       <c r="G182" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9</v>
       </c>
       <c r="G183" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9</v>
       </c>
       <c r="G184" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>7.72850322723389</v>
+        <v>7.7285041809082</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.72850322723389</v>
+        <v>7.7285041809082</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9</v>
       </c>
       <c r="G189" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9</v>
       </c>
       <c r="G190" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9</v>
       </c>
       <c r="G191" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9</v>
       </c>
       <c r="G192" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9</v>
       </c>
       <c r="G194" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9</v>
       </c>
       <c r="G195" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9</v>
       </c>
       <c r="G196" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9</v>
       </c>
       <c r="G197" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9</v>
       </c>
       <c r="G198" t="n">
-        <v>7.56049346923828</v>
+        <v>7.56049251556396</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>7.77890777587891</v>
+        <v>7.77890682220459</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>7.77890777587891</v>
+        <v>7.77890682220459</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>8.12332916259766</v>
+        <v>8.12333106994629</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G202" t="n">
-        <v>8.14852905273438</v>
+        <v>8.14853096008301</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>8.40054798126221</v>
+        <v>8.40054702758789</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>8.44254970550537</v>
+        <v>8.442551612854</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G206" t="n">
-        <v>8.45095157623291</v>
+        <v>8.45095062255859</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>8.40054798126221</v>
+        <v>8.40054702758789</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>8.52655506134033</v>
+        <v>8.52655601501465</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G209" t="n">
-        <v>8.7113676071167</v>
+        <v>8.71136856079102</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>8.64416313171387</v>
+        <v>8.64416408538818</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G211" t="n">
-        <v>8.43414974212646</v>
+        <v>8.4341516494751</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>10</v>
       </c>
       <c r="G213" t="n">
-        <v>8.40054798126221</v>
+        <v>8.40054702758789</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>10</v>
       </c>
       <c r="G214" t="n">
-        <v>8.40054798126221</v>
+        <v>8.40054702758789</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10</v>
       </c>
       <c r="G216" t="n">
-        <v>8.40054798126221</v>
+        <v>8.40054702758789</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G217" t="n">
-        <v>8.39634799957275</v>
+        <v>8.39634704589844</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G218" t="n">
-        <v>8.39214611053467</v>
+        <v>8.39214706420898</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>8.4845552444458</v>
+        <v>8.48455429077148</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.4845552444458</v>
+        <v>8.48455429077148</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G225" t="n">
-        <v>8.65256214141846</v>
+        <v>8.65256404876709</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>8.56855869293213</v>
+        <v>8.56855773925781</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.5</v>
       </c>
       <c r="G227" t="n">
-        <v>8.82057571411133</v>
+        <v>8.82057476043701</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>8.94658374786377</v>
+        <v>8.94658279418945</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.02218818664551</v>
+        <v>9.02218723297119</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G230" t="n">
-        <v>8.98858642578125</v>
+        <v>8.98858547210693</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G232" t="n">
-        <v>9.19860076904297</v>
+        <v>9.19859886169434</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G234" t="n">
-        <v>9.10619354248047</v>
+        <v>9.10619449615479</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G236" t="n">
-        <v>9.01378536224365</v>
+        <v>9.01378631591797</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G237" t="n">
-        <v>9.223801612854</v>
+        <v>9.22380065917969</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G239" t="n">
-        <v>9.04738998413086</v>
+        <v>9.04738903045654</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G240" t="n">
-        <v>9.52622222900391</v>
+        <v>9.52622127532959</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G242" t="n">
-        <v>9.40861511230469</v>
+        <v>9.40861225128174</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.40861511230469</v>
+        <v>9.40861225128174</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>9.40861511230469</v>
+        <v>9.40861225128174</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.40861511230469</v>
+        <v>9.40861225128174</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G250" t="n">
-        <v>9.40021228790283</v>
+        <v>9.40021324157715</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G252" t="n">
-        <v>9.45901775360107</v>
+        <v>9.45901679992676</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>9.40861511230469</v>
+        <v>9.40861225128174</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G261" t="n">
-        <v>9.33300876617432</v>
+        <v>9.3330078125</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G262" t="n">
-        <v>9.34140968322754</v>
+        <v>9.34140872955322</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G263" t="n">
-        <v>9.43381500244141</v>
+        <v>9.43381404876709</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G264" t="n">
-        <v>9.40021228790283</v>
+        <v>9.40021324157715</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G270" t="n">
-        <v>9.48421859741211</v>
+        <v>9.48421764373779</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>10.1646633148193</v>
+        <v>10.164662361145</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11.75</v>
       </c>
       <c r="G279" t="n">
-        <v>9.87064361572266</v>
+        <v>9.87064170837402</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11.75</v>
       </c>
       <c r="G280" t="n">
-        <v>9.87064361572266</v>
+        <v>9.87064170837402</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G281" t="n">
-        <v>9.89584445953369</v>
+        <v>9.89584541320801</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.75</v>
       </c>
       <c r="G287" t="n">
-        <v>9.87064361572266</v>
+        <v>9.87064170837402</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.75</v>
       </c>
       <c r="G289" t="n">
-        <v>9.87064361572266</v>
+        <v>9.87064170837402</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G292" t="n">
-        <v>9.92944812774658</v>
+        <v>9.92944622039795</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>9.95465087890625</v>
+        <v>9.95464897155762</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>9.61862468719482</v>
+        <v>9.61862754821777</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>9.65222835540771</v>
+        <v>9.65222930908203</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G299" t="n">
-        <v>9.62702655792236</v>
+        <v>9.62702751159668</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>9.77823829650879</v>
+        <v>9.77823734283447</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>10.0386543273926</v>
+        <v>10.0386533737183</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>10.2066669464111</v>
+        <v>10.2066640853882</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G308" t="n">
-        <v>10.3914775848389</v>
+        <v>10.3914766311646</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G309" t="n">
-        <v>10.4418802261353</v>
+        <v>10.4418792724609</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>10.4250802993774</v>
+        <v>10.4250793457031</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>12.75</v>
       </c>
       <c r="G311" t="n">
-        <v>10.7106971740723</v>
+        <v>10.7106990814209</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G312" t="n">
-        <v>10.8199062347412</v>
+        <v>10.8199052810669</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G315" t="n">
-        <v>10.9627151489258</v>
+        <v>10.9627132415771</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>13.5</v>
       </c>
       <c r="G317" t="n">
-        <v>11.3407392501831</v>
+        <v>11.3407382965088</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G318" t="n">
-        <v>11.559154510498</v>
+        <v>11.5591535568237</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G319" t="n">
-        <v>11.4835481643677</v>
+        <v>11.483549118042</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3827419281006</v>
+        <v>11.3827428817749</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G321" t="n">
-        <v>11.4919490814209</v>
+        <v>11.4919481277466</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>11.6767597198486</v>
+        <v>11.6767606735229</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G326" t="n">
-        <v>11.5675525665283</v>
+        <v>11.567554473877</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G327" t="n">
-        <v>11.5003509521484</v>
+        <v>11.5003471374512</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>11.4247446060181</v>
+        <v>11.4247455596924</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>11.4247446060181</v>
+        <v>11.4247455596924</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>11.5784425735474</v>
+        <v>11.578441619873</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G336" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979827880859</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G338" t="n">
-        <v>11.8089838027954</v>
+        <v>11.8089847564697</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>11.9626817703247</v>
+        <v>11.962682723999</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>12.2103033065796</v>
+        <v>12.2103023529053</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>11.9626817703247</v>
+        <v>11.962682723999</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>12.039529800415</v>
+        <v>12.0395278930664</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>13.75</v>
       </c>
       <c r="G347" t="n">
-        <v>11.7406749725342</v>
+        <v>11.7406768798828</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>13.75</v>
       </c>
       <c r="G348" t="n">
-        <v>11.7406749725342</v>
+        <v>11.7406768798828</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>11.6552886962891</v>
+        <v>11.6552877426147</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G351" t="n">
-        <v>11.6552886962891</v>
+        <v>11.6552877426147</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>11.5784425735474</v>
+        <v>11.578441619873</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G355" t="n">
-        <v>11.8089838027954</v>
+        <v>11.8089847564697</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>11.6552886962891</v>
+        <v>11.6552877426147</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>11.8602170944214</v>
+        <v>11.8602161407471</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G362" t="n">
-        <v>11.937066078186</v>
+        <v>11.9370651245117</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G363" t="n">
-        <v>11.937066078186</v>
+        <v>11.9370651245117</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>13.75</v>
       </c>
       <c r="G365" t="n">
-        <v>11.7406749725342</v>
+        <v>11.7406768798828</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979827880859</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8089838027954</v>
+        <v>11.8089847564697</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G371" t="n">
-        <v>11.8431396484375</v>
+        <v>11.8431386947632</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G373" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979827880859</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979827880859</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G375" t="n">
-        <v>11.7150611877441</v>
+        <v>11.7150592803955</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>11.7919063568115</v>
+        <v>11.7919073104858</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G377" t="n">
-        <v>11.7748308181763</v>
+        <v>11.7748289108276</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G380" t="n">
-        <v>11.8004465103149</v>
+        <v>11.8004446029663</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979827880859</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979827880859</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>11.6552886962891</v>
+        <v>11.6552877426147</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>11.8260622024536</v>
+        <v>11.8260641098022</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>11.5699014663696</v>
+        <v>11.5699024200439</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G388" t="n">
-        <v>11.5357475280762</v>
+        <v>11.5357484817505</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G389" t="n">
-        <v>11.5101308822632</v>
+        <v>11.5101299285889</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G391" t="n">
-        <v>11.4332847595215</v>
+        <v>11.4332828521729</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>11.4247436523438</v>
+        <v>11.4247455596924</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>11.2710466384888</v>
+        <v>11.2710485458374</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>11.185661315918</v>
+        <v>11.1856622695923</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.0917367935181</v>
+        <v>11.0917358398438</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>11.0148887634277</v>
+        <v>11.0148868560791</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G400" t="n">
-        <v>10.9636573791504</v>
+        <v>10.9636564254761</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>11.0148887634277</v>
+        <v>11.0148868560791</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G403" t="n">
-        <v>11.0319652557373</v>
+        <v>11.031964302063</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>11.0148887634277</v>
+        <v>11.0148868560791</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>10.929500579834</v>
+        <v>10.9295015335083</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G410" t="n">
-        <v>10.9892721176147</v>
+        <v>10.9892730712891</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G411" t="n">
-        <v>11.0405035018921</v>
+        <v>11.0405044555664</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>11.2710466384888</v>
+        <v>11.2710485458374</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G414" t="n">
-        <v>11.2198171615601</v>
+        <v>11.2198162078857</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>11.441822052002</v>
+        <v>11.4418230056763</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G417" t="n">
-        <v>11.4247436523438</v>
+        <v>11.4247455596924</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>13.25</v>
       </c>
       <c r="G418" t="n">
-        <v>11.3137426376343</v>
+        <v>11.31374168396</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G419" t="n">
-        <v>11.1942014694214</v>
+        <v>11.1942005157471</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G420" t="n">
-        <v>11.0661211013794</v>
+        <v>11.0661201477051</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G423" t="n">
-        <v>11.1942014694214</v>
+        <v>11.1942005157471</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>11.0575819015503</v>
+        <v>11.0575799942017</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>11.185661315918</v>
+        <v>11.1856622695923</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G428" t="n">
-        <v>11.3222799301147</v>
+        <v>11.3222808837891</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G429" t="n">
-        <v>11.1258897781372</v>
+        <v>11.1258907318115</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>11.1429691314697</v>
+        <v>11.1429672241211</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>11.0575819015503</v>
+        <v>11.0575799942017</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G432" t="n">
-        <v>11.0917367935181</v>
+        <v>11.0917358398438</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G433" t="n">
-        <v>11.2454319000244</v>
+        <v>11.2454328536987</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G436" t="n">
-        <v>10.8697309494019</v>
+        <v>10.8697299957275</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G437" t="n">
-        <v>10.9124221801758</v>
+        <v>10.9124240875244</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G438" t="n">
-        <v>11.2710466384888</v>
+        <v>11.2710485458374</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G439" t="n">
-        <v>11.3222799301147</v>
+        <v>11.3222808837891</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G440" t="n">
-        <v>10.9978113174438</v>
+        <v>10.9978122711182</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="n">
-        <v>8.93999004364014</v>
+        <v>8.93999099731445</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="n">
-        <v>9.13638114929199</v>
+        <v>9.13638019561768</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G446" t="n">
-        <v>9.40961742401123</v>
+        <v>9.40961837768555</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G447" t="n">
-        <v>9.42669486999512</v>
+        <v>9.4266939163208</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>9.13638114929199</v>
+        <v>9.13638019561768</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>9.52062225341797</v>
+        <v>9.52061939239502</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>11.25</v>
       </c>
       <c r="G451" t="n">
-        <v>9.60600757598877</v>
+        <v>9.60600662231445</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G452" t="n">
-        <v>9.48646545410156</v>
+        <v>9.48646640777588</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>9.52062225341797</v>
+        <v>9.52061939239502</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>11.25</v>
       </c>
       <c r="G454" t="n">
-        <v>9.60600757598877</v>
+        <v>9.60600662231445</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G455" t="n">
-        <v>9.3156909942627</v>
+        <v>9.31569194793701</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G456" t="n">
-        <v>9.26446056365967</v>
+        <v>9.26446151733398</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>10.75</v>
       </c>
       <c r="G457" t="n">
-        <v>9.17907428741455</v>
+        <v>9.17907333374023</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>9.22176742553711</v>
+        <v>9.22176837921143</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>9.22176742553711</v>
+        <v>9.22176837921143</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G460" t="n">
-        <v>9.33277034759521</v>
+        <v>9.3327693939209</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G461" t="n">
-        <v>9.20468902587891</v>
+        <v>9.20468807220459</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G462" t="n">
-        <v>9.16199493408203</v>
+        <v>9.16199588775635</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G464" t="n">
-        <v>8.94852828979492</v>
+        <v>8.94852924346924</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G466" t="n">
-        <v>9.18761157989502</v>
+        <v>9.18761253356934</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G468" t="n">
-        <v>9.57185077667236</v>
+        <v>9.571852684021</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>9.56331539154053</v>
+        <v>9.56331253051758</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G472" t="n">
-        <v>9.58893013000488</v>
+        <v>9.58892917633057</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G473" t="n">
-        <v>9.67431545257568</v>
+        <v>9.67431735992432</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G474" t="n">
-        <v>9.63162326812744</v>
+        <v>9.63162231445312</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G475" t="n">
-        <v>9.40961742401123</v>
+        <v>9.40961837768555</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G477" t="n">
-        <v>9.16199493408203</v>
+        <v>9.16199588775635</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G478" t="n">
-        <v>9.16199493408203</v>
+        <v>9.16199588775635</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>10.75</v>
       </c>
       <c r="G479" t="n">
-        <v>9.17907428741455</v>
+        <v>9.17907333374023</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G482" t="n">
-        <v>9.06807041168213</v>
+        <v>9.06807136535645</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>9.04245471954346</v>
+        <v>9.04245567321777</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G484" t="n">
-        <v>9.75116539001465</v>
+        <v>9.75116443634033</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870071411133</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>9.56331539154053</v>
+        <v>9.56331253051758</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>11.5</v>
       </c>
       <c r="G489" t="n">
-        <v>9.81947231292725</v>
+        <v>9.81947326660156</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G490" t="n">
-        <v>9.75116539001465</v>
+        <v>9.75116443634033</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>9.6913948059082</v>
+        <v>9.69139385223389</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>9.56331539154053</v>
+        <v>9.56331253051758</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G494" t="n">
-        <v>9.58893013000488</v>
+        <v>9.58892917633057</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="n">
-        <v>9.41815662384033</v>
+        <v>9.41815757751465</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="n">
-        <v>9.33277034759521</v>
+        <v>9.3327693939209</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G497" t="n">
-        <v>9.57185077667236</v>
+        <v>9.571852684021</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>11.25</v>
       </c>
       <c r="G499" t="n">
-        <v>9.60600757598877</v>
+        <v>9.60600662231445</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G500" t="n">
-        <v>9.50354194641113</v>
+        <v>9.50354385375977</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>11</v>
       </c>
       <c r="G501" t="n">
-        <v>9.39253997802734</v>
+        <v>9.39254093170166</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>11</v>
       </c>
       <c r="G505" t="n">
-        <v>9.39253997802734</v>
+        <v>9.39254093170166</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G508" t="n">
-        <v>9.04245471954346</v>
+        <v>9.04245567321777</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>9.13638114929199</v>
+        <v>9.13638019561768</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>9.13638114929199</v>
+        <v>9.13638019561768</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G511" t="n">
-        <v>9.15345764160156</v>
+        <v>9.15345859527588</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G512" t="n">
-        <v>9.22176742553711</v>
+        <v>9.22176837921143</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>9.13638114929199</v>
+        <v>9.13638019561768</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>10.75</v>
       </c>
       <c r="G514" t="n">
-        <v>9.17907428741455</v>
+        <v>9.17907333374023</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>10.75</v>
       </c>
       <c r="G516" t="n">
-        <v>9.17907428741455</v>
+        <v>9.17907333374023</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>11</v>
       </c>
       <c r="G518" t="n">
-        <v>9.39253997802734</v>
+        <v>9.39254093170166</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G520" t="n">
-        <v>9.43523216247559</v>
+        <v>9.43523406982422</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G521" t="n">
-        <v>9.56331539154053</v>
+        <v>9.56331253051758</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G522" t="n">
-        <v>9.52062225341797</v>
+        <v>9.52061939239502</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>9.52062225341797</v>
+        <v>9.52061939239502</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>9.43523216247559</v>
+        <v>9.43523406982422</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.25</v>
       </c>
       <c r="G526" t="n">
-        <v>9.60600757598877</v>
+        <v>9.60600662231445</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G527" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870071411133</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G528" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870071411133</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>11.25</v>
       </c>
       <c r="G529" t="n">
-        <v>9.60600757598877</v>
+        <v>9.60600662231445</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870071411133</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>11.5</v>
       </c>
       <c r="G531" t="n">
-        <v>9.81947231292725</v>
+        <v>9.81947326660156</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870071411133</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G533" t="n">
-        <v>9.776780128479</v>
+        <v>9.77677917480469</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G539" t="n">
-        <v>9.13638114929199</v>
+        <v>9.13638019561768</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>9.13638114929199</v>
+        <v>9.13638019561768</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>8.83752822875977</v>
+        <v>8.83752632141113</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G551" t="n">
-        <v>8.92291259765625</v>
+        <v>8.92291355133057</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>10.25</v>
       </c>
       <c r="G554" t="n">
-        <v>8.7521390914917</v>
+        <v>8.75214004516602</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>8.62406158447266</v>
+        <v>8.62405967712402</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>10.25</v>
       </c>
       <c r="G556" t="n">
-        <v>8.7521390914917</v>
+        <v>8.75214004516602</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>8.83752822875977</v>
+        <v>8.83752632141113</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>8.83752822875977</v>
+        <v>8.83752632141113</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>8.79483222961426</v>
+        <v>8.79483318328857</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>10.25</v>
       </c>
       <c r="G567" t="n">
-        <v>8.7521390914917</v>
+        <v>8.75214004516602</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>8.66675186157227</v>
+        <v>8.6667537689209</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>10.25</v>
       </c>
       <c r="G569" t="n">
-        <v>8.7521390914917</v>
+        <v>8.75214004516602</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G570" t="n">
-        <v>8.92291259765625</v>
+        <v>8.92291355133057</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>8.66675186157227</v>
+        <v>8.6667537689209</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>10</v>
       </c>
       <c r="G572" t="n">
-        <v>8.53867435455322</v>
+        <v>8.53867244720459</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G575" t="n">
-        <v>8.79483222961426</v>
+        <v>8.79483318328857</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>8.62406158447266</v>
+        <v>8.62405967712402</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>10</v>
       </c>
       <c r="G579" t="n">
-        <v>8.53867435455322</v>
+        <v>8.53867244720459</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G581" t="n">
-        <v>8.62406158447266</v>
+        <v>8.62405967712402</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>10.25</v>
       </c>
       <c r="G582" t="n">
-        <v>8.7521390914917</v>
+        <v>8.75214004516602</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>8.83752822875977</v>
+        <v>8.83752632141113</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>8.92291259765625</v>
+        <v>8.92291355133057</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>9.13638114929199</v>
+        <v>9.13638019561768</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>8.92291259765625</v>
+        <v>8.92291355133057</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>8.79483222961426</v>
+        <v>8.79483318328857</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>8.79483222961426</v>
+        <v>8.79483318328857</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>8.83752822875977</v>
+        <v>8.83752632141113</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>8.83752822875977</v>
+        <v>8.83752632141113</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G599" t="n">
-        <v>9.02945709228516</v>
+        <v>9.02945613861084</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>9.02945709228516</v>
+        <v>9.02945613861084</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>9.02945709228516</v>
+        <v>9.02945613861084</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>8.68921852111816</v>
+        <v>8.68921566009521</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G614" t="n">
-        <v>8.4100456237793</v>
+        <v>8.41004657745361</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G615" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G616" t="n">
-        <v>8.5496301651001</v>
+        <v>8.54963111877441</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G617" t="n">
-        <v>8.51473331451416</v>
+        <v>8.51473522186279</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G618" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>8.58452701568604</v>
+        <v>8.58452796936035</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G620" t="n">
-        <v>8.53218269348145</v>
+        <v>8.53218173980713</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G621" t="n">
-        <v>8.65432071685791</v>
+        <v>8.65431976318359</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>8.65432071685791</v>
+        <v>8.65431976318359</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G623" t="n">
-        <v>8.61942577362061</v>
+        <v>8.61942386627197</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G624" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>8.68921852111816</v>
+        <v>8.68921566009521</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G627" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176914215088</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>8.5496301651001</v>
+        <v>8.54963111877441</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G629" t="n">
-        <v>8.53218269348145</v>
+        <v>8.53218173980713</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>8.46238803863525</v>
+        <v>8.46238899230957</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G632" t="n">
-        <v>8.20066452026367</v>
+        <v>8.2006664276123</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>8.25301170349121</v>
+        <v>8.25301074981689</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G635" t="n">
-        <v>8.51473331451416</v>
+        <v>8.51473522186279</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G636" t="n">
-        <v>8.5496301651001</v>
+        <v>8.54963111877441</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G638" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G640" t="n">
-        <v>8.61942577362061</v>
+        <v>8.61942386627197</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G642" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G644" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>8.68921852111816</v>
+        <v>8.68921566009521</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>8.68921852111816</v>
+        <v>8.68921566009521</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G649" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176914215088</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G650" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G651" t="n">
-        <v>8.68921852111816</v>
+        <v>8.68921566009521</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G655" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176914215088</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G656" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176914215088</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G657" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>8.58452701568604</v>
+        <v>8.58452796936035</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>8.61942577362061</v>
+        <v>8.61942386627197</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G660" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>8.58452701568604</v>
+        <v>8.58452796936035</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G676" t="n">
-        <v>8.60197639465332</v>
+        <v>8.60197353363037</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G677" t="n">
-        <v>8.61942577362061</v>
+        <v>8.61942386627197</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G680" t="n">
-        <v>8.65432071685791</v>
+        <v>8.65431976318359</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G682" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176914215088</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>8.5496301651001</v>
+        <v>8.54963111877441</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G684" t="n">
-        <v>8.46238803863525</v>
+        <v>8.46238899230957</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G687" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G688" t="n">
-        <v>8.61942577362061</v>
+        <v>8.61942386627197</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G693" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>8.65432071685791</v>
+        <v>8.65431976318359</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>9.29118061065674</v>
+        <v>9.29117965698242</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>9.24755954742432</v>
+        <v>9.24756050109863</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G704" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G705" t="n">
-        <v>9.07307624816895</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>9.07307624816895</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G707" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G710" t="n">
-        <v>8.60197639465332</v>
+        <v>8.60197353363037</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G711" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.58452701568604</v>
+        <v>8.58452796936035</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G714" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G715" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G718" t="n">
-        <v>8.65432071685791</v>
+        <v>8.65431976318359</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G730" t="n">
-        <v>8.60197639465332</v>
+        <v>8.60197353363037</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G731" t="n">
-        <v>8.61942577362061</v>
+        <v>8.61942386627197</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G732" t="n">
-        <v>8.46238803863525</v>
+        <v>8.46238899230957</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G733" t="n">
-        <v>8.46238803863525</v>
+        <v>8.46238899230957</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G734" t="n">
-        <v>8.39259719848633</v>
+        <v>8.39259624481201</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G735" t="n">
-        <v>8.34025192260742</v>
+        <v>8.34025287628174</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G736" t="n">
-        <v>8.42749214172363</v>
+        <v>8.42749309539795</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G737" t="n">
-        <v>8.4100456237793</v>
+        <v>8.41004657745361</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G739" t="n">
-        <v>8.4100456237793</v>
+        <v>8.41004657745361</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G740" t="n">
-        <v>8.27045726776123</v>
+        <v>8.27045822143555</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G742" t="n">
-        <v>8.23556232452393</v>
+        <v>8.23556327819824</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>8.25301170349121</v>
+        <v>8.25301074981689</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G744" t="n">
-        <v>8.23556232452393</v>
+        <v>8.23556327819824</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G745" t="n">
-        <v>8.27045726776123</v>
+        <v>8.27045822143555</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G746" t="n">
-        <v>8.06107902526855</v>
+        <v>8.06107997894287</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G748" t="n">
-        <v>8.27045726776123</v>
+        <v>8.27045822143555</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G750" t="n">
-        <v>8.09597682952881</v>
+        <v>8.09597778320312</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G751" t="n">
-        <v>8.20066452026367</v>
+        <v>8.2006664276123</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G752" t="n">
-        <v>8.20066452026367</v>
+        <v>8.2006664276123</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G754" t="n">
-        <v>8.14832019805908</v>
+        <v>8.14832210540771</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G756" t="n">
-        <v>8.20066452026367</v>
+        <v>8.2006664276123</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G759" t="n">
-        <v>8.20066452026367</v>
+        <v>8.2006664276123</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G760" t="n">
-        <v>8.06107902526855</v>
+        <v>8.06107997894287</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G761" t="n">
-        <v>8.14832019805908</v>
+        <v>8.14832210540771</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G763" t="n">
-        <v>8.18321800231934</v>
+        <v>8.18321704864502</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G770" t="n">
-        <v>8.4449405670166</v>
+        <v>8.44494152069092</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G771" t="n">
-        <v>8.61942577362061</v>
+        <v>8.61942386627197</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G772" t="n">
-        <v>8.53218269348145</v>
+        <v>8.53218173980713</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G773" t="n">
-        <v>8.63687038421631</v>
+        <v>8.63687133789062</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G775" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>8.81135368347168</v>
+        <v>8.81135559082031</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G779" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G781" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G787" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G789" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>9.24755954742432</v>
+        <v>9.24756050109863</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>9.07307624816895</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G796" t="n">
-        <v>9.20393943786621</v>
+        <v>9.20393848419189</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G798" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>8.76773548126221</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G805" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G806" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>9.07307624816895</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>9.07307624816895</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583698272705</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>9.07307624816895</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G814" t="n">
-        <v>8.89859580993652</v>
+        <v>8.89859485626221</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G816" t="n">
-        <v>9.33480072021484</v>
+        <v>9.33480167388916</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>9.552903175354</v>
+        <v>9.55290508270264</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>9.552903175354</v>
+        <v>9.55290508270264</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>11.25</v>
       </c>
       <c r="G820" t="n">
-        <v>9.81462669372559</v>
+        <v>9.8146276473999</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5</v>
       </c>
       <c r="G821" t="n">
-        <v>10.0327301025391</v>
+        <v>10.0327291488647</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>10.0763502120972</v>
+        <v>10.0763511657715</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>11.5</v>
       </c>
       <c r="G823" t="n">
-        <v>10.0327301025391</v>
+        <v>10.0327291488647</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>10.2072114944458</v>
+        <v>10.2072124481201</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>10.2072114944458</v>
+        <v>10.2072124481201</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3380746841431</v>
+        <v>10.3380737304688</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>11.25</v>
       </c>
       <c r="G841" t="n">
-        <v>9.81462669372559</v>
+        <v>9.8146276473999</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>11.5</v>
       </c>
       <c r="G843" t="n">
-        <v>10.0327301025391</v>
+        <v>10.0327291488647</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.5</v>
       </c>
       <c r="G844" t="n">
-        <v>10.0327301025391</v>
+        <v>10.0327291488647</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G847" t="n">
-        <v>10.425313949585</v>
+        <v>10.4253149032593</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>10.380763053894</v>
+        <v>10.3807640075684</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>10.6035242080688</v>
+        <v>10.6035251617432</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="n">
-        <v>10.5144195556641</v>
+        <v>10.5144205093384</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>10.5144195556641</v>
+        <v>10.5144205093384</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>10.380763053894</v>
+        <v>10.3807640075684</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="n">
-        <v>10.157998085022</v>
+        <v>10.1579990386963</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>10.380763053894</v>
+        <v>10.3807640075684</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>10.5144195556641</v>
+        <v>10.5144205093384</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>10.2025508880615</v>
+        <v>10.2025527954102</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G876" t="n">
-        <v>10.2025508880615</v>
+        <v>10.2025527954102</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134471893311</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>10.157998085022</v>
+        <v>10.1579990386963</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G880" t="n">
-        <v>10.2025508880615</v>
+        <v>10.2025527954102</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>10.2025508880615</v>
+        <v>10.2025527954102</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>10.2025508880615</v>
+        <v>10.2025527954102</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>10.157998085022</v>
+        <v>10.1579990386963</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>9.89068412780762</v>
+        <v>9.89068508148193</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>11.25</v>
       </c>
       <c r="G886" t="n">
-        <v>10.0243425369263</v>
+        <v>10.024341583252</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.25</v>
       </c>
       <c r="G887" t="n">
-        <v>10.0243425369263</v>
+        <v>10.024341583252</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134471893311</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134471893311</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G890" t="n">
-        <v>10.157998085022</v>
+        <v>10.1579990386963</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134471893311</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134471893311</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G893" t="n">
-        <v>10.2025508880615</v>
+        <v>10.2025527954102</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>11.25</v>
       </c>
       <c r="G895" t="n">
-        <v>10.0243425369263</v>
+        <v>10.024341583252</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.25</v>
       </c>
       <c r="G898" t="n">
-        <v>10.0243425369263</v>
+        <v>10.024341583252</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.89068412780762</v>
+        <v>9.89068508148193</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>9.89068412780762</v>
+        <v>9.89068508148193</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>11</v>
       </c>
       <c r="G902" t="n">
-        <v>9.80157852172852</v>
+        <v>9.8015775680542</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11</v>
       </c>
       <c r="G905" t="n">
-        <v>9.80157852172852</v>
+        <v>9.8015775680542</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>9.89068412780762</v>
+        <v>9.89068508148193</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.25</v>
       </c>
       <c r="G908" t="n">
-        <v>10.0243425369263</v>
+        <v>10.024341583252</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>10.157998085022</v>
+        <v>10.1579990386963</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>10.157998085022</v>
+        <v>10.1579990386963</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G912" t="n">
-        <v>10.157998085022</v>
+        <v>10.1579990386963</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134471893311</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>11.25</v>
       </c>
       <c r="G914" t="n">
-        <v>10.0243425369263</v>
+        <v>10.024341583252</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>11.25</v>
       </c>
       <c r="G915" t="n">
-        <v>10.0243425369263</v>
+        <v>10.024341583252</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>11.25</v>
       </c>
       <c r="G917" t="n">
-        <v>10.0243425369263</v>
+        <v>10.024341583252</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>11.25</v>
       </c>
       <c r="G919" t="n">
-        <v>10.0243425369263</v>
+        <v>10.024341583252</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>9.93523597717285</v>
+        <v>9.93523502349854</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>9.93523597717285</v>
+        <v>9.93523502349854</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G922" t="n">
-        <v>9.66792106628418</v>
+        <v>9.66792011260986</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>9.62336730957031</v>
+        <v>9.62336826324463</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>11</v>
       </c>
       <c r="G924" t="n">
-        <v>9.80157852172852</v>
+        <v>9.8015775680542</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G931" t="n">
-        <v>9.53426361083984</v>
+        <v>9.53426265716553</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G933" t="n">
-        <v>9.53426361083984</v>
+        <v>9.53426265716553</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>9.04418468475342</v>
+        <v>9.04418277740479</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>8.95507907867432</v>
+        <v>8.955078125</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>9.04418468475342</v>
+        <v>9.04418277740479</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G945" t="n">
-        <v>8.95507907867432</v>
+        <v>8.955078125</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>9.04418468475342</v>
+        <v>9.04418277740479</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>9.08873653411865</v>
+        <v>9.08873462677002</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>9.04418468475342</v>
+        <v>9.04418277740479</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>9.08873653411865</v>
+        <v>9.08873462677002</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>9.04418468475342</v>
+        <v>9.04418277740479</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>9.08873653411865</v>
+        <v>9.08873462677002</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G964" t="n">
-        <v>9.04418468475342</v>
+        <v>9.04418277740479</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>9.04418468475342</v>
+        <v>9.04418277740479</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>9.48970985412598</v>
+        <v>9.48970890045166</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>10.75</v>
       </c>
       <c r="G987" t="n">
-        <v>9.57881450653076</v>
+        <v>9.57881546020508</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G992" t="n">
-        <v>10.5144195556641</v>
+        <v>10.5144205093384</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>12.75</v>
       </c>
       <c r="G994" t="n">
-        <v>11.3609209060669</v>
+        <v>11.3609199523926</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G995" t="n">
-        <v>11.4054746627808</v>
+        <v>11.4054727554321</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>11.04905128479</v>
+        <v>11.0490503311157</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G998" t="n">
-        <v>10.8262882232666</v>
+        <v>10.8262891769409</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>10.7817373275757</v>
+        <v>10.7817363739014</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>12.25</v>
       </c>
       <c r="G1000" t="n">
-        <v>10.91539478302</v>
+        <v>10.9153938293457</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>11.3163681030273</v>
+        <v>11.316367149353</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>11.4054746627808</v>
+        <v>11.4054727554321</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1006" t="n">
-        <v>11.6727895736694</v>
+        <v>11.6727905273438</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>13.25</v>
       </c>
       <c r="G1007" t="n">
-        <v>11.8064470291138</v>
+        <v>11.8064460754395</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>11.8955526351929</v>
+        <v>11.8955535888672</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>11.7173414230347</v>
+        <v>11.7173404693604</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>11.4054746627808</v>
+        <v>11.4054727554321</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>11.7173414230347</v>
+        <v>11.7173404693604</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>11.7173414230347</v>
+        <v>11.7173404693604</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1019" t="n">
-        <v>11.7173414230347</v>
+        <v>11.7173404693604</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1020" t="n">
-        <v>11.6727895736694</v>
+        <v>11.6727905273438</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>13.25</v>
       </c>
       <c r="G1021" t="n">
-        <v>11.8064470291138</v>
+        <v>11.8064460754395</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>11.8955526351929</v>
+        <v>11.8955535888672</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>11.8955526351929</v>
+        <v>11.8955535888672</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>11.7173414230347</v>
+        <v>11.7173404693604</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.2074193954468</v>
+        <v>12.2074213027954</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1028" t="n">
-        <v>12.8311586380005</v>
+        <v>12.8311567306519</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.652946472168</v>
+        <v>12.6529474258423</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>12.8311586380005</v>
+        <v>12.8311567306519</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.4301824569702</v>
+        <v>12.4301834106445</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>12.1628665924072</v>
+        <v>12.1628675460815</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1038" t="n">
-        <v>11.8955526351929</v>
+        <v>11.8955535888672</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.2965259552002</v>
+        <v>12.2965250015259</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1040" t="n">
-        <v>12.2074193954468</v>
+        <v>12.2074213027954</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1041" t="n">
-        <v>12.2965259552002</v>
+        <v>12.2965250015259</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>12.5638408660889</v>
+        <v>12.5638418197632</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.5638408660889</v>
+        <v>12.5638418197632</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.7866058349609</v>
+        <v>12.7866048812866</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1048" t="n">
-        <v>12.7866058349609</v>
+        <v>12.7866048812866</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1049" t="n">
-        <v>12.8311586380005</v>
+        <v>12.8311567306519</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1051" t="n">
-        <v>12.652946472168</v>
+        <v>12.6529474258423</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>13.25</v>
       </c>
       <c r="G1053" t="n">
-        <v>11.8064470291138</v>
+        <v>11.8064460754395</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>13.25</v>
       </c>
       <c r="G1054" t="n">
-        <v>11.8064470291138</v>
+        <v>11.8064460754395</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>13.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>11.8064470291138</v>
+        <v>11.8064460754395</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>11.7173414230347</v>
+        <v>11.7173404693604</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>11.6282377243042</v>
+        <v>11.6282348632812</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>11.6282377243042</v>
+        <v>11.6282348632812</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>12</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.6926317214966</v>
+        <v>10.6926326751709</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>11.75</v>
       </c>
       <c r="G1061" t="n">
-        <v>10.4698677062988</v>
+        <v>10.4698667526245</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>10.75</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.57881450653076</v>
+        <v>9.57881546020508</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1066" t="n">
-        <v>8.82141971588135</v>
+        <v>8.82142066955566</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>7.75215625762939</v>
+        <v>7.75215816497803</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.46702003479004</v>
+        <v>7.46702098846436</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.82344198226929</v>
+        <v>7.82344102859497</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1073" t="n">
-        <v>7.89472579956055</v>
+        <v>7.89472532272339</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1075" t="n">
-        <v>8.53628253936768</v>
+        <v>8.53628444671631</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.58974838256836</v>
+        <v>8.58974742889404</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>9.04418468475342</v>
+        <v>9.04418277740479</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>10.25</v>
       </c>
       <c r="G1080" t="n">
-        <v>9.13328838348389</v>
+        <v>9.1332893371582</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.95507907867432</v>
+        <v>8.955078125</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>9.08873653411865</v>
+        <v>9.08873462677002</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1086" t="n">
-        <v>9.66792106628418</v>
+        <v>9.66792011260986</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1087" t="n">
-        <v>9.66792106628418</v>
+        <v>9.66792011260986</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1090" t="n">
-        <v>9.62336730957031</v>
+        <v>9.62336826324463</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1092" t="n">
-        <v>9.66792106628418</v>
+        <v>9.66792011260986</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>10.75</v>
       </c>
       <c r="G1093" t="n">
-        <v>9.57881450653076</v>
+        <v>9.57881546020508</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>11</v>
       </c>
       <c r="G1094" t="n">
-        <v>9.80157852172852</v>
+        <v>9.8015775680542</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1095" t="n">
-        <v>9.62336730957031</v>
+        <v>9.62336826324463</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>9.66792106628418</v>
+        <v>9.66792011260986</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1098" t="n">
-        <v>10.2025508880615</v>
+        <v>10.2025527954102</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>9.85371494293213</v>
+        <v>9.85371589660645</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1101" t="n">
-        <v>9.71685791015625</v>
+        <v>9.71685600280762</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>10.75</v>
       </c>
       <c r="G1102" t="n">
-        <v>9.80809497833252</v>
+        <v>9.80809593200684</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1106" t="n">
-        <v>9.62561893463135</v>
+        <v>9.62561988830566</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.76247787475586</v>
+        <v>9.76247596740723</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1109" t="n">
-        <v>9.62561893463135</v>
+        <v>9.62561988830566</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1114" t="n">
-        <v>10.3099040985107</v>
+        <v>10.3099050521851</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1116" t="n">
-        <v>10.3099040985107</v>
+        <v>10.3099050521851</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1117" t="n">
-        <v>10.2186679840088</v>
+        <v>10.2186660766602</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>10.6292371749878</v>
+        <v>10.6292390823364</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>11.5</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.4923820495605</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1121" t="n">
-        <v>10.5836191177368</v>
+        <v>10.5836200714111</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>10.5380010604858</v>
+        <v>10.5380001068115</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1125" t="n">
-        <v>10.6292371749878</v>
+        <v>10.6292390823364</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1126" t="n">
-        <v>10.5380010604858</v>
+        <v>10.5380001068115</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1128" t="n">
-        <v>10.5836191177368</v>
+        <v>10.5836200714111</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>10.5836191177368</v>
+        <v>10.5836200714111</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>11.5</v>
       </c>
       <c r="G1131" t="n">
-        <v>10.4923820495605</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.5836191177368</v>
+        <v>10.5836200714111</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>11.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.4923820495605</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>10.2186679840088</v>
+        <v>10.2186660766602</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.6292371749878</v>
+        <v>10.6292390823364</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1141" t="n">
-        <v>11.2222862243652</v>
+        <v>11.2222852706909</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.2222862243652</v>
+        <v>11.2222852706909</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>12.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>11.4047613143921</v>
+        <v>11.4047632217407</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1144" t="n">
-        <v>11.0854272842407</v>
+        <v>11.085428237915</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>12.25</v>
       </c>
       <c r="G1146" t="n">
-        <v>11.1766662597656</v>
+        <v>11.1766672134399</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.2222862243652</v>
+        <v>11.2222852706909</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.8573341369629</v>
+        <v>10.8573331832886</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.0854272842407</v>
+        <v>11.085428237915</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>10.9941911697388</v>
+        <v>10.9941902160645</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>10.8573341369629</v>
+        <v>10.8573331832886</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>11.75</v>
       </c>
       <c r="G1154" t="n">
-        <v>10.720477104187</v>
+        <v>10.7204761505127</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1159" t="n">
-        <v>10.8117141723633</v>
+        <v>10.8117151260376</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.6292371749878</v>
+        <v>10.6292390823364</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>11.75</v>
       </c>
       <c r="G1163" t="n">
-        <v>10.720477104187</v>
+        <v>10.7204761505127</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1164" t="n">
-        <v>10.8573341369629</v>
+        <v>10.8573331832886</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1165" t="n">
-        <v>11.3135242462158</v>
+        <v>11.3135223388672</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>11.3135242462158</v>
+        <v>11.3135223388672</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>11.0854272842407</v>
+        <v>11.085428237915</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1169" t="n">
-        <v>11.1310472488403</v>
+        <v>11.1310482025146</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>11.0854272842407</v>
+        <v>11.085428237915</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>11.0854272842407</v>
+        <v>11.085428237915</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1172" t="n">
-        <v>11.1310472488403</v>
+        <v>11.1310482025146</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.2222862243652</v>
+        <v>11.2222852706909</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>12.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>11.1766662597656</v>
+        <v>11.1766672134399</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>10.8573341369629</v>
+        <v>10.8573331832886</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>11.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.4923820495605</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>11.75</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.720477104187</v>
+        <v>10.7204761505127</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>11.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>10.4923820495605</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>11.75</v>
       </c>
       <c r="G1186" t="n">
-        <v>10.720477104187</v>
+        <v>10.7204761505127</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>10.8573341369629</v>
+        <v>10.8573331832886</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1190" t="n">
-        <v>10.8573341369629</v>
+        <v>10.8573331832886</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1193" t="n">
-        <v>10.8117141723633</v>
+        <v>10.8117151260376</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>11.75</v>
       </c>
       <c r="G1194" t="n">
-        <v>10.720477104187</v>
+        <v>10.7204761505127</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1196" t="n">
-        <v>10.9941911697388</v>
+        <v>10.9941902160645</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>12.25</v>
       </c>
       <c r="G1197" t="n">
-        <v>11.1766662597656</v>
+        <v>11.1766672134399</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1199" t="n">
-        <v>11.2679071426392</v>
+        <v>11.2679061889648</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1200" t="n">
-        <v>11.2222862243652</v>
+        <v>11.2222852706909</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.450382232666</v>
+        <v>11.4503812789917</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>11.1310472488403</v>
+        <v>11.1310482025146</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>11.5872373580933</v>
+        <v>11.5872383117676</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>11.5872373580933</v>
+        <v>11.5872383117676</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>11.3135242462158</v>
+        <v>11.3135223388672</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>13</v>
       </c>
       <c r="G1208" t="n">
-        <v>11.8609523773193</v>
+        <v>11.8609533309937</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1209" t="n">
-        <v>11.6784772872925</v>
+        <v>11.6784763336182</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>11.9978103637695</v>
+        <v>11.9978084564209</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>11.7240962982178</v>
+        <v>11.7240972518921</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13</v>
       </c>
       <c r="G1215" t="n">
-        <v>11.8609523773193</v>
+        <v>11.8609533309937</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>11.7697143554688</v>
+        <v>11.7697134017944</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>11.5872373580933</v>
+        <v>11.5872383117676</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>11.7697143554688</v>
+        <v>11.7697134017944</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>11.6784772872925</v>
+        <v>11.6784763336182</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1221" t="n">
-        <v>11.7697143554688</v>
+        <v>11.7697134017944</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>11.7697143554688</v>
+        <v>11.7697134017944</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.7240962982178</v>
+        <v>11.7240972518921</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>13</v>
       </c>
       <c r="G1226" t="n">
-        <v>11.8609523773193</v>
+        <v>11.8609533309937</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>11.450382232666</v>
+        <v>11.4503812789917</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1230" t="n">
-        <v>11.5872373580933</v>
+        <v>11.5872383117676</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.6784772872925</v>
+        <v>11.6784763336182</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.7697143554688</v>
+        <v>11.7697134017944</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>14</v>
       </c>
       <c r="G1239" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>14.25</v>
       </c>
       <c r="G1244" t="n">
-        <v>13.0014295578003</v>
+        <v>13.001428604126</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1245" t="n">
-        <v>13.0470495223999</v>
+        <v>13.0470485687256</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1246" t="n">
-        <v>13.2751426696777</v>
+        <v>13.2751436233521</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1248" t="n">
-        <v>13.1839036941528</v>
+        <v>13.1839056015015</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>12.8645706176758</v>
+        <v>12.8645725250244</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1250" t="n">
-        <v>13.0470495223999</v>
+        <v>13.0470485687256</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>13.3207635879517</v>
+        <v>13.3207626342773</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>13.3207635879517</v>
+        <v>13.3207626342773</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1255" t="n">
-        <v>13.0470495223999</v>
+        <v>13.0470485687256</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1256" t="n">
-        <v>12.8645706176758</v>
+        <v>12.8645725250244</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>14</v>
       </c>
       <c r="G1259" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>12.8645706176758</v>
+        <v>12.8645725250244</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>14</v>
       </c>
       <c r="G1262" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>14</v>
       </c>
       <c r="G1263" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>14</v>
       </c>
       <c r="G1264" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1265" t="n">
-        <v>12.4083814620972</v>
+        <v>12.4083824157715</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1270" t="n">
-        <v>12.7277154922485</v>
+        <v>12.7277145385742</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>14</v>
       </c>
       <c r="G1272" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1273" t="n">
-        <v>12.7277154922485</v>
+        <v>12.7277145385742</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>14</v>
       </c>
       <c r="G1278" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>14</v>
       </c>
       <c r="G1282" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>12.6364765167236</v>
+        <v>12.6364774703979</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1284" t="n">
-        <v>12.4083814620972</v>
+        <v>12.4083824157715</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>12.4083814620972</v>
+        <v>12.4083824157715</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>13.75</v>
       </c>
       <c r="G1286" t="n">
-        <v>12.5452394485474</v>
+        <v>12.545238494873</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>14</v>
       </c>
       <c r="G1288" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>14</v>
       </c>
       <c r="G1289" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1291" t="n">
-        <v>12.7277154922485</v>
+        <v>12.7277145385742</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1293" t="n">
-        <v>13.0470495223999</v>
+        <v>13.0470485687256</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>14.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>13.2295246124268</v>
+        <v>13.2295236587524</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1296" t="n">
-        <v>13.7313356399536</v>
+        <v>13.731333732605</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1297" t="n">
-        <v>13.8225727081299</v>
+        <v>13.8225717544556</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>14.0506677627563</v>
+        <v>14.050666809082</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>14.2331438064575</v>
+        <v>14.2331428527832</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>14.2331438064575</v>
+        <v>14.2331428527832</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.5524768829346</v>
+        <v>14.5524749755859</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1309" t="n">
-        <v>14.9174280166626</v>
+        <v>14.9174299240112</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>14.4156188964844</v>
+        <v>14.4156198501587</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1312" t="n">
-        <v>14.3243818283081</v>
+        <v>14.3243808746338</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>14.2331438064575</v>
+        <v>14.2331428527832</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.2331438064575</v>
+        <v>14.2331428527832</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1316" t="n">
-        <v>14.3243818283081</v>
+        <v>14.3243808746338</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>15.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>14.1419057846069</v>
+        <v>14.1419048309326</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>15.5</v>
       </c>
       <c r="G1318" t="n">
-        <v>14.1419057846069</v>
+        <v>14.1419048309326</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1319" t="n">
-        <v>14.4156188964844</v>
+        <v>14.4156198501587</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1320" t="n">
-        <v>13.8681898117065</v>
+        <v>13.8681907653809</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>14</v>
       </c>
       <c r="G1327" t="n">
-        <v>12.7733345031738</v>
+        <v>12.7733335494995</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1328" t="n">
-        <v>13.1839036941528</v>
+        <v>13.1839056015015</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>15</v>
       </c>
       <c r="G1330" t="n">
-        <v>13.6857137680054</v>
+        <v>13.6857147216797</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>14.0506677627563</v>
+        <v>14.050666809082</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>15</v>
       </c>
       <c r="G1334" t="n">
-        <v>13.6857137680054</v>
+        <v>13.6857147216797</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>13.7313356399536</v>
+        <v>13.731333732605</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>13.6400947570801</v>
+        <v>13.6400957107544</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>15</v>
       </c>
       <c r="G1337" t="n">
-        <v>13.6857137680054</v>
+        <v>13.6857147216797</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1338" t="n">
-        <v>14.2331438064575</v>
+        <v>14.2331428527832</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1339" t="n">
-        <v>14.4156188964844</v>
+        <v>14.4156198501587</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1340" t="n">
-        <v>14.5524768829346</v>
+        <v>14.5524749755859</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>16.25</v>
       </c>
       <c r="G1341" t="n">
-        <v>14.8261919021606</v>
+        <v>14.826189994812</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>14.9174280166626</v>
+        <v>14.9174299240112</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1344" t="n">
-        <v>14.3243818283081</v>
+        <v>14.3243808746338</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1345" t="n">
-        <v>14.0506677627563</v>
+        <v>14.050666809082</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1346" t="n">
-        <v>14.3243818283081</v>
+        <v>14.3243808746338</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>14.3243818283081</v>
+        <v>14.3243808746338</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>15.5</v>
       </c>
       <c r="G1348" t="n">
-        <v>14.1419057846069</v>
+        <v>14.1419048309326</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1349" t="n">
-        <v>13.8225727081299</v>
+        <v>13.8225717544556</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.8681898117065</v>
+        <v>13.8681907653809</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1352" t="n">
-        <v>13.8225727081299</v>
+        <v>13.8225717544556</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1354" t="n">
-        <v>14.3039169311523</v>
+        <v>14.303915977478</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1356" t="n">
-        <v>14.3503570556641</v>
+        <v>14.3503580093384</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>14.9540948867798</v>
+        <v>14.9540939331055</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>15.18630027771</v>
+        <v>15.1863021850586</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>15.75</v>
       </c>
       <c r="G1382" t="n">
-        <v>14.6290054321289</v>
+        <v>14.6290044784546</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1383" t="n">
-        <v>14.6754465103149</v>
+        <v>14.6754474639893</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>16.25</v>
       </c>
       <c r="G1384" t="n">
-        <v>15.0934190750122</v>
+        <v>15.0934181213379</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>16.75</v>
       </c>
       <c r="G1387" t="n">
-        <v>15.5578317642212</v>
+        <v>15.5578327178955</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1392" t="n">
-        <v>15.6507139205933</v>
+        <v>15.6507158279419</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1394" t="n">
-        <v>15.9758033752441</v>
+        <v>15.9758014678955</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1395" t="n">
-        <v>15.9758033752441</v>
+        <v>15.9758014678955</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1398" t="n">
-        <v>15.9758033752441</v>
+        <v>15.9758014678955</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>18</v>
       </c>
       <c r="G1400" t="n">
-        <v>16.7188625335693</v>
+        <v>16.718864440918</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>18</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.7188625335693</v>
+        <v>16.718864440918</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1405" t="n">
-        <v>17.1368370056152</v>
+        <v>17.1368350982666</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>17.75</v>
       </c>
       <c r="G1410" t="n">
-        <v>16.4866580963135</v>
+        <v>16.4866561889648</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>18.25</v>
       </c>
       <c r="G1411" t="n">
-        <v>16.9510707855225</v>
+        <v>16.9510688781738</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1412" t="n">
-        <v>17.1368370056152</v>
+        <v>17.1368350982666</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1413" t="n">
-        <v>17.3690414428711</v>
+        <v>17.3690433502197</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>19.25</v>
       </c>
       <c r="G1417" t="n">
-        <v>17.8798942565918</v>
+        <v>17.8798961639404</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>18.3907489776611</v>
+        <v>18.3907508850098</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>18.3907489776611</v>
+        <v>18.3907508850098</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>20</v>
       </c>
       <c r="G1420" t="n">
-        <v>18.5765151977539</v>
+        <v>18.5765132904053</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>20.5</v>
       </c>
       <c r="G1426" t="n">
-        <v>19.0409278869629</v>
+        <v>19.0409297943115</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>21</v>
       </c>
       <c r="G1428" t="n">
-        <v>19.5053405761719</v>
+        <v>19.5053386688232</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>19.6911067962646</v>
+        <v>19.6911087036133</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1434" t="n">
-        <v>20.8056983947754</v>
+        <v>20.8056964874268</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1435" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>22.5</v>
       </c>
       <c r="G1436" t="n">
-        <v>20.8985786437988</v>
+        <v>20.8985767364502</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>22.5</v>
       </c>
       <c r="G1438" t="n">
-        <v>20.8985786437988</v>
+        <v>20.8985767364502</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1439" t="n">
-        <v>20.8056983947754</v>
+        <v>20.8056964874268</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>20.6199321746826</v>
+        <v>20.6199340820312</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>20.8056983947754</v>
+        <v>20.8056964874268</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>22.5</v>
       </c>
       <c r="G1444" t="n">
-        <v>20.8985786437988</v>
+        <v>20.8985767364502</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>21.641637802124</v>
+        <v>21.6416397094727</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>23.5</v>
       </c>
       <c r="G1449" t="n">
-        <v>21.8274059295654</v>
+        <v>21.8274040222168</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>23.5</v>
       </c>
       <c r="G1450" t="n">
-        <v>21.8274059295654</v>
+        <v>21.8274040222168</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1452" t="n">
-        <v>22.1060543060303</v>
+        <v>22.1060523986816</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.4558773040771</v>
+        <v>21.4558753967285</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>22.1060543060303</v>
+        <v>22.1060523986816</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>18.1585426330566</v>
+        <v>18.1585445404053</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.8551635742188</v>
+        <v>18.8551616668701</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>22</v>
       </c>
       <c r="G1467" t="n">
-        <v>20.4341678619385</v>
+        <v>20.4341659545898</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.6911067962646</v>
+        <v>19.6911087036133</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>21.7345218658447</v>
+        <v>21.7345199584961</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1475" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1478" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1479" t="n">
-        <v>22.570463180542</v>
+        <v>22.5704650878906</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>22.570463180542</v>
+        <v>22.5704650878906</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1484" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1485" t="n">
-        <v>20.9914608001709</v>
+        <v>20.9914627075195</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>20.9914608001709</v>
+        <v>20.9914627075195</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1488" t="n">
-        <v>20.9914608001709</v>
+        <v>20.9914627075195</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1495" t="n">
-        <v>20.8056983947754</v>
+        <v>20.8056964874268</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1496" t="n">
-        <v>20.9914608001709</v>
+        <v>20.9914627075195</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1497" t="n">
-        <v>20.8056983947754</v>
+        <v>20.8056964874268</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1498" t="n">
-        <v>20.8056983947754</v>
+        <v>20.8056964874268</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>22</v>
       </c>
       <c r="G1499" t="n">
-        <v>20.4341678619385</v>
+        <v>20.4341659545898</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1500" t="n">
-        <v>20.6199321746826</v>
+        <v>20.6199340820312</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1501" t="n">
-        <v>20.3412818908691</v>
+        <v>20.3412837982178</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>19.8768730163574</v>
+        <v>19.8768711090088</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1505" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1506" t="n">
-        <v>20.8056983947754</v>
+        <v>20.8056964874268</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1508" t="n">
-        <v>20.3412818908691</v>
+        <v>20.3412837982178</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>20.9914608001709</v>
+        <v>20.9914627075195</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>23.5</v>
       </c>
       <c r="G1510" t="n">
-        <v>21.8274059295654</v>
+        <v>21.8274040222168</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>23.5</v>
       </c>
       <c r="G1514" t="n">
-        <v>21.8274059295654</v>
+        <v>21.8274040222168</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.9914608001709</v>
+        <v>20.9914627075195</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1518" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1520" t="n">
-        <v>21.4558773040771</v>
+        <v>21.4558753967285</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>22.4775848388672</v>
+        <v>22.4775829315186</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1523" t="n">
-        <v>22.1989345550537</v>
+        <v>22.1989364624023</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1529" t="n">
-        <v>21.4558773040771</v>
+        <v>21.4558753967285</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>22.5</v>
       </c>
       <c r="G1530" t="n">
-        <v>20.8985786437988</v>
+        <v>20.8985767364502</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>20.3412818908691</v>
+        <v>20.3412837982178</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>19.8768730163574</v>
+        <v>19.8768711090088</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>19.7839889526367</v>
+        <v>19.7839870452881</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>22</v>
       </c>
       <c r="G1536" t="n">
-        <v>20.4341678619385</v>
+        <v>20.4341659545898</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1537" t="n">
-        <v>20.9914608001709</v>
+        <v>20.9914627075195</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1538" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1539" t="n">
-        <v>20.3412818908691</v>
+        <v>20.3412837982178</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1540" t="n">
-        <v>20.3412818908691</v>
+        <v>20.3412837982178</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1541" t="n">
-        <v>20.2483997344971</v>
+        <v>20.2483978271484</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>20.5</v>
       </c>
       <c r="G1543" t="n">
-        <v>19.0409278869629</v>
+        <v>19.0409297943115</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1546" t="n">
-        <v>20.3412818908691</v>
+        <v>20.3412837982178</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>20.9914608001709</v>
+        <v>20.9914627075195</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1549" t="n">
-        <v>20.9914608001709</v>
+        <v>20.9914627075195</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>22</v>
       </c>
       <c r="G1550" t="n">
-        <v>20.4341678619385</v>
+        <v>20.4341659545898</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1554" t="n">
-        <v>19.6911067962646</v>
+        <v>19.6911087036133</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1556" t="n">
-        <v>19.6911067962646</v>
+        <v>19.6911087036133</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1558" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1561" t="n">
-        <v>19.2266960144043</v>
+        <v>19.2266941070557</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1563" t="n">
-        <v>20.8056983947754</v>
+        <v>20.8056964874268</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1564" t="n">
-        <v>19.2266960144043</v>
+        <v>19.2266941070557</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1565" t="n">
-        <v>18.669397354126</v>
+        <v>18.6693992614746</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1566" t="n">
-        <v>19.6911067962646</v>
+        <v>19.6911087036133</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1568" t="n">
-        <v>18.2049865722656</v>
+        <v>18.204984664917</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1569" t="n">
-        <v>18.669397354126</v>
+        <v>18.6693992614746</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>18</v>
       </c>
       <c r="G1570" t="n">
-        <v>16.7188625335693</v>
+        <v>16.718864440918</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1572" t="n">
-        <v>14.6754465103149</v>
+        <v>14.6754474639893</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>15.9758033752441</v>
+        <v>15.9758014678955</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1585" t="n">
-        <v>17.22971534729</v>
+        <v>17.2297191619873</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1588" t="n">
-        <v>17.7870140075684</v>
+        <v>17.7870121002197</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>19.5</v>
       </c>
       <c r="G1590" t="n">
-        <v>18.1121006011963</v>
+        <v>18.1121025085449</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1595" t="n">
-        <v>18.0563735961914</v>
+        <v>18.0563716888428</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1599" t="n">
-        <v>17.9634914398193</v>
+        <v>17.9634895324707</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>20</v>
       </c>
       <c r="G1600" t="n">
-        <v>18.5765151977539</v>
+        <v>18.5765132904053</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>20.25</v>
       </c>
       <c r="G1601" t="n">
-        <v>18.8087196350098</v>
+        <v>18.808723449707</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1603" t="n">
-        <v>19.7839889526367</v>
+        <v>19.7839870452881</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1608" t="n">
-        <v>20.0161972045898</v>
+        <v>20.0161952972412</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>21.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.9697532653809</v>
+        <v>19.9697551727295</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>20</v>
       </c>
       <c r="G1610" t="n">
-        <v>18.5765151977539</v>
+        <v>18.5765132904053</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1612" t="n">
-        <v>17.3690414428711</v>
+        <v>17.3690433502197</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1613" t="n">
-        <v>17.4061946868896</v>
+        <v>17.406192779541</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>68.8000030517578</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>19664</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>70</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>68</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>69.6999969482422</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>69.1999969482422</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>69.1999969482422</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -63262,7 +63262,7 @@
         <v>16900</v>
       </c>
       <c r="C2735" t="n">
-        <v>69.6999969482422</v>
+        <v>69.8000030517578</v>
       </c>
       <c r="D2735" t="n">
         <v>67.5999984741211</v>
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>69.5</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>69.8000030517578</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>69.6999969482422</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>70.0999984741211</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>70.0999984741211</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>71.3000030517578</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>30641</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>71.8000030517578</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>67.6999969482422</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>70.9000015258789</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>70.9000015258789</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>68.1999969482422</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>18306</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>67.4000015258789</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>65.6999969482422</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>67.3000030517578</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>67.3000030517578</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>67.0999984741211</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>37664</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>69.9000015258789</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>65.8000030517578</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>67.1999969482422</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>29046</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>70.8000030517578</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>69.0999984741211</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>70.1999969482422</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>69.4000015258789</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10207271575928</v>
+        <v>8.10207176208496</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G17" t="n">
-        <v>7.97039651870728</v>
+        <v>7.97039890289307</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>8.01566028594971</v>
+        <v>8.01566219329834</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G19" t="n">
-        <v>7.99920129776001</v>
+        <v>7.99920034408569</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G20" t="n">
-        <v>7.90044641494751</v>
+        <v>7.90044498443604</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G21" t="n">
-        <v>7.9498233795166</v>
+        <v>7.94982242584229</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>7.84695434570312</v>
+        <v>7.84695386886597</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G26" t="n">
-        <v>7.84283876419067</v>
+        <v>7.84283685684204</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.5</v>
       </c>
       <c r="G27" t="n">
-        <v>7.81815052032471</v>
+        <v>7.81814956665039</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.5</v>
       </c>
       <c r="G28" t="n">
-        <v>7.81815052032471</v>
+        <v>7.81814956665039</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.5</v>
       </c>
       <c r="G29" t="n">
-        <v>7.81815052032471</v>
+        <v>7.81814956665039</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G30" t="n">
-        <v>7.80992031097412</v>
+        <v>7.80992078781128</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G31" t="n">
-        <v>7.80992031097412</v>
+        <v>7.80992078781128</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.5</v>
       </c>
       <c r="G32" t="n">
-        <v>7.81815052032471</v>
+        <v>7.81814956665039</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.5</v>
       </c>
       <c r="G33" t="n">
-        <v>7.81815052032471</v>
+        <v>7.81814956665039</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.5</v>
       </c>
       <c r="G34" t="n">
-        <v>7.81815052032471</v>
+        <v>7.81814956665039</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.5</v>
       </c>
       <c r="G35" t="n">
-        <v>7.81815052032471</v>
+        <v>7.81814956665039</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.5</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81815052032471</v>
+        <v>7.81814956665039</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.5</v>
       </c>
       <c r="G37" t="n">
-        <v>7.81815052032471</v>
+        <v>7.81814956665039</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80992031097412</v>
+        <v>7.80992078781128</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>7.78523111343384</v>
+        <v>7.785231590271</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G40" t="n">
-        <v>7.58360433578491</v>
+        <v>7.58360576629639</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G41" t="n">
-        <v>7.65355634689331</v>
+        <v>7.65355777740479</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G42" t="n">
-        <v>7.63709592819214</v>
+        <v>7.63709783554077</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G43" t="n">
-        <v>7.62475252151489</v>
+        <v>7.62475347518921</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.55480289459229</v>
+        <v>7.55480194091797</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G45" t="n">
-        <v>7.49307775497437</v>
+        <v>7.49307727813721</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G49" t="n">
-        <v>7.70293474197388</v>
+        <v>7.7029333114624</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G50" t="n">
-        <v>7.73585319519043</v>
+        <v>7.73585176467896</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>7.78523111343384</v>
+        <v>7.785231590271</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>7.78523111343384</v>
+        <v>7.785231590271</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>7.78523111343384</v>
+        <v>7.785231590271</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>7.78523111343384</v>
+        <v>7.785231590271</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>7.78523111343384</v>
+        <v>7.785231590271</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G57" t="n">
-        <v>7.9498233795166</v>
+        <v>7.94982242584229</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G58" t="n">
-        <v>8.03211975097656</v>
+        <v>8.03212070465088</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99920129776001</v>
+        <v>7.99920034408569</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G62" t="n">
-        <v>7.98274326324463</v>
+        <v>7.982741355896</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>7.98274326324463</v>
+        <v>7.982741355896</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>7.98274326324463</v>
+        <v>7.982741355896</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>7.98274326324463</v>
+        <v>7.982741355896</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G70" t="n">
-        <v>7.93336391448975</v>
+        <v>7.93336486816406</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G71" t="n">
-        <v>7.89221572875977</v>
+        <v>7.89221620559692</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.84283876419067</v>
+        <v>7.84283685684204</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G76" t="n">
-        <v>8.03211975097656</v>
+        <v>8.03212070465088</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G77" t="n">
-        <v>8.14733600616455</v>
+        <v>8.14733409881592</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="G78" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="G79" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="G81" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10</v>
       </c>
       <c r="G82" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10</v>
       </c>
       <c r="G84" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G85" t="n">
-        <v>8.22140216827393</v>
+        <v>8.22139930725098</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>10</v>
       </c>
       <c r="G86" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>10</v>
       </c>
       <c r="G87" t="n">
-        <v>8.22962951660156</v>
+        <v>8.22963237762451</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>8.08972835540771</v>
+        <v>8.0897274017334</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>8.35854530334473</v>
+        <v>8.35854434967041</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G93" t="n">
-        <v>8.08132648468018</v>
+        <v>8.08132743835449</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G94" t="n">
-        <v>8.10652732849121</v>
+        <v>8.10652923583984</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G95" t="n">
-        <v>8.13593006134033</v>
+        <v>8.13593101501465</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G97" t="n">
-        <v>8.10652732849121</v>
+        <v>8.10652923583984</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G98" t="n">
-        <v>8.10652732849121</v>
+        <v>8.10652923583984</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>8.04772472381592</v>
+        <v>8.04772567749023</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G100" t="n">
-        <v>8.14853191375732</v>
+        <v>8.14852905273438</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>8.14853191375732</v>
+        <v>8.14852905273438</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>8.14012908935547</v>
+        <v>8.14013004302979</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G103" t="n">
-        <v>8.14433097839355</v>
+        <v>8.14433002471924</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.75</v>
       </c>
       <c r="G106" t="n">
-        <v>8.19053268432617</v>
+        <v>8.19053363800049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.75</v>
       </c>
       <c r="G107" t="n">
-        <v>8.19053268432617</v>
+        <v>8.19053363800049</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.75</v>
       </c>
       <c r="G108" t="n">
-        <v>8.19053268432617</v>
+        <v>8.19053363800049</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.75</v>
       </c>
       <c r="G109" t="n">
-        <v>8.19053268432617</v>
+        <v>8.19053363800049</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.75</v>
       </c>
       <c r="G110" t="n">
-        <v>8.19053268432617</v>
+        <v>8.19053363800049</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.75</v>
       </c>
       <c r="G111" t="n">
-        <v>8.19053268432617</v>
+        <v>8.19053363800049</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.75</v>
       </c>
       <c r="G112" t="n">
-        <v>8.19053268432617</v>
+        <v>8.19053363800049</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.75</v>
       </c>
       <c r="G113" t="n">
-        <v>8.19053268432617</v>
+        <v>8.19053363800049</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.75</v>
       </c>
       <c r="G114" t="n">
-        <v>8.19053268432617</v>
+        <v>8.19053363800049</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>8.02252292633057</v>
+        <v>8.0225248336792</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.02252292633057</v>
+        <v>8.0225248336792</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G120" t="n">
-        <v>8.03932285308838</v>
+        <v>8.0393238067627</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.5</v>
       </c>
       <c r="G121" t="n">
-        <v>7.98051977157593</v>
+        <v>7.98052072525024</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>8.02252292633057</v>
+        <v>8.0225248336792</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>8.10652732849121</v>
+        <v>8.10652923583984</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G124" t="n">
-        <v>8.10652732849121</v>
+        <v>8.10652923583984</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G125" t="n">
-        <v>7.89651393890381</v>
+        <v>7.89651346206665</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G126" t="n">
-        <v>7.85451316833496</v>
+        <v>7.85451126098633</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G127" t="n">
-        <v>7.81251001358032</v>
+        <v>7.81250953674316</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>7.81251001358032</v>
+        <v>7.81250953674316</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G131" t="n">
-        <v>7.85451316833496</v>
+        <v>7.85451126098633</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G132" t="n">
-        <v>7.85451316833496</v>
+        <v>7.85451126098633</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G133" t="n">
-        <v>7.85451316833496</v>
+        <v>7.85451126098633</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.5</v>
       </c>
       <c r="G134" t="n">
-        <v>7.98051977157593</v>
+        <v>7.98052072525024</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.05612468719482</v>
+        <v>8.05612564086914</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G137" t="n">
-        <v>8.05612468719482</v>
+        <v>8.05612564086914</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.05612468719482</v>
+        <v>8.05612564086914</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>8.05612468719482</v>
+        <v>8.05612564086914</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.05612468719482</v>
+        <v>8.05612564086914</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>8.05612468719482</v>
+        <v>8.05612564086914</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>8.05612468719482</v>
+        <v>8.05612564086914</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G143" t="n">
-        <v>8.05612468719482</v>
+        <v>8.05612564086914</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G144" t="n">
-        <v>8.10652732849121</v>
+        <v>8.10652923583984</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G145" t="n">
-        <v>7.89651393890381</v>
+        <v>7.89651346206665</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>7.867112159729</v>
+        <v>7.86711311340332</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>7.81251001358032</v>
+        <v>7.81250953674316</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>7.81251001358032</v>
+        <v>7.81250953674316</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.64449977874756</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G152" t="n">
-        <v>7.64449977874756</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G153" t="n">
-        <v>7.64449977874756</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G154" t="n">
-        <v>7.64449977874756</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G155" t="n">
-        <v>7.64449977874756</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G157" t="n">
-        <v>7.64449977874756</v>
+        <v>7.6444993019104</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G166" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G167" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G168" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G172" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G174" t="n">
-        <v>7.87131357192993</v>
+        <v>7.87131261825562</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G175" t="n">
-        <v>7.74530458450317</v>
+        <v>7.74530506134033</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G176" t="n">
-        <v>7.74530458450317</v>
+        <v>7.74530506134033</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G177" t="n">
-        <v>7.74530458450317</v>
+        <v>7.74530506134033</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G178" t="n">
-        <v>7.74530458450317</v>
+        <v>7.74530506134033</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G179" t="n">
-        <v>7.74530458450317</v>
+        <v>7.74530506134033</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>7.72850322723389</v>
+        <v>7.72850275039673</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9</v>
       </c>
       <c r="G181" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9</v>
       </c>
       <c r="G182" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9</v>
       </c>
       <c r="G183" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9</v>
       </c>
       <c r="G184" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>7.72850322723389</v>
+        <v>7.72850275039673</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.72850322723389</v>
+        <v>7.72850275039673</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>7.60249614715576</v>
+        <v>7.60249519348145</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>7.60249614715576</v>
+        <v>7.60249519348145</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9</v>
       </c>
       <c r="G189" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9</v>
       </c>
       <c r="G190" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9</v>
       </c>
       <c r="G191" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9</v>
       </c>
       <c r="G192" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>7.60249614715576</v>
+        <v>7.60249519348145</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9</v>
       </c>
       <c r="G194" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9</v>
       </c>
       <c r="G195" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9</v>
       </c>
       <c r="G196" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9</v>
       </c>
       <c r="G197" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9</v>
       </c>
       <c r="G198" t="n">
-        <v>7.56049203872681</v>
+        <v>7.56049346923828</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>7.77890825271606</v>
+        <v>7.77890682220459</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>7.77890825271606</v>
+        <v>7.77890682220459</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>8.12332916259766</v>
+        <v>8.12333011627197</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G202" t="n">
-        <v>8.14853191375732</v>
+        <v>8.14852905273438</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G203" t="n">
-        <v>8.35854530334473</v>
+        <v>8.35854434967041</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>8.52655410766602</v>
+        <v>8.52655601501465</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G209" t="n">
-        <v>8.71136665344238</v>
+        <v>8.7113676071167</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G212" t="n">
-        <v>8.46775245666504</v>
+        <v>8.46775150299072</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>8.35854530334473</v>
+        <v>8.35854434967041</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G219" t="n">
-        <v>8.46775245666504</v>
+        <v>8.46775150299072</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>8.48455429077148</v>
+        <v>8.48455333709717</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.48455429077148</v>
+        <v>8.48455333709717</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G222" t="n">
-        <v>8.5013542175293</v>
+        <v>8.50135231018066</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>8.73656845092773</v>
+        <v>8.73656940460205</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>8.73656845092773</v>
+        <v>8.73656940460205</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>8.56855773925781</v>
+        <v>8.56855869293213</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.5</v>
       </c>
       <c r="G227" t="n">
-        <v>8.8205738067627</v>
+        <v>8.82057571411133</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>8.94658279418945</v>
+        <v>8.94658184051514</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>9.02218723297119</v>
+        <v>9.02218818664551</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G230" t="n">
-        <v>8.98858451843262</v>
+        <v>8.98858642578125</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.75</v>
       </c>
       <c r="G231" t="n">
-        <v>9.03058815002441</v>
+        <v>9.03058910369873</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G232" t="n">
-        <v>9.19859790802002</v>
+        <v>9.19859981536865</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>9.11459636688232</v>
+        <v>9.11459350585938</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G234" t="n">
-        <v>9.10619354248047</v>
+        <v>9.10619449615479</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G235" t="n">
-        <v>8.99698734283447</v>
+        <v>8.99698638916016</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G236" t="n">
-        <v>9.0137882232666</v>
+        <v>9.01378726959229</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G237" t="n">
-        <v>9.223801612854</v>
+        <v>9.22380065917969</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G239" t="n">
-        <v>9.04739093780518</v>
+        <v>9.04739189147949</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G240" t="n">
-        <v>9.52622127532959</v>
+        <v>9.52622222900391</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G241" t="n">
-        <v>9.32460784912109</v>
+        <v>9.32460880279541</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G242" t="n">
-        <v>9.40861225128174</v>
+        <v>9.40861320495605</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.40861225128174</v>
+        <v>9.40861320495605</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>9.40861225128174</v>
+        <v>9.40861320495605</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>9.32460784912109</v>
+        <v>9.32460880279541</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G246" t="n">
-        <v>9.30780506134033</v>
+        <v>9.30780792236328</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G247" t="n">
-        <v>9.30780506134033</v>
+        <v>9.30780792236328</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.40861225128174</v>
+        <v>9.40861320495605</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G250" t="n">
-        <v>9.40021324157715</v>
+        <v>9.40021228790283</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>9.36661052703857</v>
+        <v>9.36660957336426</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>9.36661052703857</v>
+        <v>9.36660957336426</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>9.36661052703857</v>
+        <v>9.36660957336426</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G255" t="n">
-        <v>9.30780506134033</v>
+        <v>9.30780792236328</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>9.32460784912109</v>
+        <v>9.32460880279541</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>9.36661052703857</v>
+        <v>9.36660957336426</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>9.40861225128174</v>
+        <v>9.40861320495605</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>9.49261951446533</v>
+        <v>9.49262046813965</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G260" t="n">
-        <v>9.39181327819824</v>
+        <v>9.39181232452393</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G261" t="n">
-        <v>9.33300876617432</v>
+        <v>9.3330078125</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G263" t="n">
-        <v>9.43381500244141</v>
+        <v>9.43381404876709</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G264" t="n">
-        <v>9.40021324157715</v>
+        <v>9.40021228790283</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>9.49261951446533</v>
+        <v>9.49262046813965</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>9.49261951446533</v>
+        <v>9.49262046813965</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G267" t="n">
-        <v>9.49261951446533</v>
+        <v>9.49262046813965</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G268" t="n">
-        <v>9.49261951446533</v>
+        <v>9.49262046813965</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G269" t="n">
-        <v>9.49261951446533</v>
+        <v>9.49262046813965</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G270" t="n">
-        <v>9.48421859741211</v>
+        <v>9.48421955108643</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>10.1646633148193</v>
+        <v>10.1646614074707</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>9.91264724731445</v>
+        <v>9.9126443862915</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>9.91264724731445</v>
+        <v>9.9126443862915</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G284" t="n">
-        <v>9.82863998413086</v>
+        <v>9.82864093780518</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.82863998413086</v>
+        <v>9.82864093780518</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>9.82863998413086</v>
+        <v>9.82864093780518</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>9.82863998413086</v>
+        <v>9.82864093780518</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>9.82863998413086</v>
+        <v>9.82864093780518</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>9.82863998413086</v>
+        <v>9.82864093780518</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>9.91264724731445</v>
+        <v>9.9126443862915</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>9.9546480178833</v>
+        <v>9.95464992523193</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>9.61862754821777</v>
+        <v>9.61862468719482</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G298" t="n">
-        <v>9.65222930908203</v>
+        <v>9.6522274017334</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G299" t="n">
-        <v>9.62702751159668</v>
+        <v>9.62702655792236</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>9.49261951446533</v>
+        <v>9.49262046813965</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>9.82863998413086</v>
+        <v>9.82864093780518</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G302" t="n">
-        <v>9.99665069580078</v>
+        <v>9.9966516494751</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>9.99665069580078</v>
+        <v>9.9966516494751</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G304" t="n">
-        <v>9.77823638916016</v>
+        <v>9.77823829650879</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>9.91264724731445</v>
+        <v>9.9126443862915</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>10.0386552810669</v>
+        <v>10.0386533737183</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>10.2066650390625</v>
+        <v>10.2066640853882</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>12.75</v>
       </c>
       <c r="G311" t="n">
-        <v>10.7106971740723</v>
+        <v>10.7107000350952</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G313" t="n">
-        <v>10.7695026397705</v>
+        <v>10.7695016860962</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>13</v>
       </c>
       <c r="G314" t="n">
-        <v>10.9207124710083</v>
+        <v>10.9207105636597</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G315" t="n">
-        <v>10.9627141952515</v>
+        <v>10.9627151489258</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>13.5</v>
       </c>
       <c r="G317" t="n">
-        <v>11.3407392501831</v>
+        <v>11.3407411575317</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G319" t="n">
-        <v>11.4835472106934</v>
+        <v>11.4835481643677</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>11.6011581420898</v>
+        <v>11.6011571884155</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>11.6767616271973</v>
+        <v>11.6767606735229</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G324" t="n">
-        <v>11.7103633880615</v>
+        <v>11.7103614807129</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G325" t="n">
-        <v>11.7355651855469</v>
+        <v>11.7355642318726</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G327" t="n">
-        <v>11.5003499984741</v>
+        <v>11.5003509521484</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.5</v>
       </c>
       <c r="G332" t="n">
-        <v>11.5272102355957</v>
+        <v>11.5272092819214</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>11.6296720504761</v>
+        <v>11.6296710968018</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G335" t="n">
-        <v>11.578441619873</v>
+        <v>11.5784425735474</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G336" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979808807373</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>11.7833681106567</v>
+        <v>11.7833700180054</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G338" t="n">
-        <v>11.8089847564697</v>
+        <v>11.8089838027954</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>11.9626817703247</v>
+        <v>11.9626808166504</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>12.2103023529053</v>
+        <v>12.210301399231</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>14</v>
       </c>
       <c r="G342" t="n">
-        <v>11.9541416168213</v>
+        <v>11.9541435241699</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>11.9626817703247</v>
+        <v>11.9626808166504</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G346" t="n">
-        <v>11.6296720504761</v>
+        <v>11.6296710968018</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>13.75</v>
       </c>
       <c r="G347" t="n">
-        <v>11.7406740188599</v>
+        <v>11.7406749725342</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>13.75</v>
       </c>
       <c r="G348" t="n">
-        <v>11.7406740188599</v>
+        <v>11.7406749725342</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>11.7833681106567</v>
+        <v>11.7833700180054</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>11.578441619873</v>
+        <v>11.5784425735474</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>14</v>
       </c>
       <c r="G354" t="n">
-        <v>11.9541416168213</v>
+        <v>11.9541435241699</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G355" t="n">
-        <v>11.8089847564697</v>
+        <v>11.8089838027954</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G357" t="n">
-        <v>11.7492141723633</v>
+        <v>11.7492151260376</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>11.7833681106567</v>
+        <v>11.7833700180054</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14</v>
       </c>
       <c r="G359" t="n">
-        <v>11.9541416168213</v>
+        <v>11.9541435241699</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G360" t="n">
-        <v>11.8175230026245</v>
+        <v>11.8175239562988</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G361" t="n">
-        <v>11.8602161407471</v>
+        <v>11.8602180480957</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G362" t="n">
-        <v>11.9370651245117</v>
+        <v>11.937066078186</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G363" t="n">
-        <v>11.9370651245117</v>
+        <v>11.937066078186</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.9456043243408</v>
+        <v>11.9456033706665</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>13.75</v>
       </c>
       <c r="G365" t="n">
-        <v>11.7406740188599</v>
+        <v>11.7406749725342</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979808807373</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>11.6894445419312</v>
+        <v>11.6894435882568</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8089847564697</v>
+        <v>11.8089838027954</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G369" t="n">
-        <v>11.9285268783569</v>
+        <v>11.9285259246826</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G370" t="n">
-        <v>11.7833681106567</v>
+        <v>11.7833700180054</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G371" t="n">
-        <v>11.8431386947632</v>
+        <v>11.8431396484375</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G372" t="n">
-        <v>11.7833681106567</v>
+        <v>11.7833700180054</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G373" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979808807373</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979808807373</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G375" t="n">
-        <v>11.7150611877441</v>
+        <v>11.7150621414185</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G376" t="n">
-        <v>11.7919082641602</v>
+        <v>11.7919073104858</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G378" t="n">
-        <v>11.723596572876</v>
+        <v>11.7235975265503</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G379" t="n">
-        <v>11.7662916183472</v>
+        <v>11.7662897109985</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G380" t="n">
-        <v>11.8004455566406</v>
+        <v>11.8004465103149</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8175230026245</v>
+        <v>11.8175239562988</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979808807373</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>11.6979818344116</v>
+        <v>11.6979808807373</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G386" t="n">
-        <v>11.6211338043213</v>
+        <v>11.6211347579956</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>11.5699005126953</v>
+        <v>11.5699014663696</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G389" t="n">
-        <v>11.5101299285889</v>
+        <v>11.5101308822632</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G391" t="n">
-        <v>11.4332828521729</v>
+        <v>11.4332838058472</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>11.4247436523438</v>
+        <v>11.4247446060181</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>11.185661315918</v>
+        <v>11.1856622695923</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13</v>
       </c>
       <c r="G397" t="n">
-        <v>11.1002750396729</v>
+        <v>11.1002759933472</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.0917348861694</v>
+        <v>11.0917358398438</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>11.0148878097534</v>
+        <v>11.0148887634277</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>11.0148878097534</v>
+        <v>11.0148887634277</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>11.0148878097534</v>
+        <v>11.0148887634277</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>13</v>
       </c>
       <c r="G405" t="n">
-        <v>11.1002750396729</v>
+        <v>11.1002759933472</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>13</v>
       </c>
       <c r="G406" t="n">
-        <v>11.1002750396729</v>
+        <v>11.1002759933472</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>10.8441133499146</v>
+        <v>10.8441152572632</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>10.9721965789795</v>
+        <v>10.9721946716309</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G410" t="n">
-        <v>10.9892730712891</v>
+        <v>10.9892721176147</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>11.441822052002</v>
+        <v>11.4418210983276</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G417" t="n">
-        <v>11.4247436523438</v>
+        <v>11.4247446060181</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G419" t="n">
-        <v>11.1942014694214</v>
+        <v>11.1942005157471</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G420" t="n">
-        <v>11.0661191940308</v>
+        <v>11.0661211013794</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>13</v>
       </c>
       <c r="G421" t="n">
-        <v>11.1002750396729</v>
+        <v>11.1002759933472</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G423" t="n">
-        <v>11.1942014694214</v>
+        <v>11.1942005157471</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>11.0575819015503</v>
+        <v>11.0575828552246</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="n">
-        <v>10.9465780258179</v>
+        <v>10.9465789794922</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>11.185661315918</v>
+        <v>11.1856622695923</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G429" t="n">
-        <v>11.1258916854858</v>
+        <v>11.1258907318115</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>11.1429681777954</v>
+        <v>11.1429691314697</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>11.0575819015503</v>
+        <v>11.0575828552246</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G432" t="n">
-        <v>11.0917348861694</v>
+        <v>11.0917358398438</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G433" t="n">
-        <v>11.2454319000244</v>
+        <v>11.2454328536987</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13</v>
       </c>
       <c r="G434" t="n">
-        <v>11.1002750396729</v>
+        <v>11.1002759933472</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G437" t="n">
-        <v>10.9124250411987</v>
+        <v>10.9124240875244</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G440" t="n">
-        <v>10.9978103637695</v>
+        <v>10.9978113174438</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>10.9721965789795</v>
+        <v>10.9721946716309</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G442" t="n">
-        <v>9.65723991394043</v>
+        <v>9.65723896026611</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="n">
-        <v>9.13638019561768</v>
+        <v>9.13638114929199</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G445" t="n">
-        <v>9.29861640930176</v>
+        <v>9.29861354827881</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G446" t="n">
-        <v>9.40961647033691</v>
+        <v>9.40961742401123</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G447" t="n">
-        <v>9.42669486999512</v>
+        <v>9.42669582366943</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>9.13638019561768</v>
+        <v>9.13638114929199</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G452" t="n">
-        <v>9.48646450042725</v>
+        <v>9.48646545410156</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G455" t="n">
-        <v>9.3156909942627</v>
+        <v>9.31569290161133</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G456" t="n">
-        <v>9.26445960998535</v>
+        <v>9.26446056365967</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>10.75</v>
       </c>
       <c r="G457" t="n">
-        <v>9.17907333374023</v>
+        <v>9.17907524108887</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>9.22176837921143</v>
+        <v>9.22176742553711</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>9.22176837921143</v>
+        <v>9.22176742553711</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>9.05099487304688</v>
+        <v>9.05099391937256</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G464" t="n">
-        <v>8.94852924346924</v>
+        <v>8.94852828979492</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G465" t="n">
-        <v>9.12784290313721</v>
+        <v>9.12784194946289</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G466" t="n">
-        <v>9.18761253356934</v>
+        <v>9.18761157989502</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G469" t="n">
-        <v>9.58039093017578</v>
+        <v>9.58039283752441</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>9.56331348419189</v>
+        <v>9.56331443786621</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>9.65723991394043</v>
+        <v>9.65723896026611</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G472" t="n">
-        <v>9.58892822265625</v>
+        <v>9.58892917633057</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G473" t="n">
-        <v>9.67431545257568</v>
+        <v>9.67431640625</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G474" t="n">
-        <v>9.63162517547607</v>
+        <v>9.63162231445312</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G475" t="n">
-        <v>9.40961647033691</v>
+        <v>9.40961742401123</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G476" t="n">
-        <v>9.12784290313721</v>
+        <v>9.12784194946289</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>10.75</v>
       </c>
       <c r="G479" t="n">
-        <v>9.17907333374023</v>
+        <v>9.17907524108887</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G481" t="n">
-        <v>8.86314296722412</v>
+        <v>8.86314392089844</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G483" t="n">
-        <v>9.04245567321777</v>
+        <v>9.04245471954346</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G484" t="n">
-        <v>9.75116348266602</v>
+        <v>9.75116443634033</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G485" t="n">
-        <v>9.58039093017578</v>
+        <v>9.58039283752441</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870262145996</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G487" t="n">
-        <v>9.58039093017578</v>
+        <v>9.58039283752441</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>9.56331348419189</v>
+        <v>9.56331443786621</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>11.5</v>
       </c>
       <c r="G489" t="n">
-        <v>9.81947326660156</v>
+        <v>9.81947422027588</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G490" t="n">
-        <v>9.75116348266602</v>
+        <v>9.75116443634033</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>9.6913948059082</v>
+        <v>9.69139385223389</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>9.56331348419189</v>
+        <v>9.56331443786621</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G493" t="n">
-        <v>9.45231056213379</v>
+        <v>9.45231151580811</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G494" t="n">
-        <v>9.58892822265625</v>
+        <v>9.58892917633057</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G498" t="n">
-        <v>9.49500465393066</v>
+        <v>9.49500370025635</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G500" t="n">
-        <v>9.50354194641113</v>
+        <v>9.50354290008545</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>11</v>
       </c>
       <c r="G501" t="n">
-        <v>9.39253902435303</v>
+        <v>9.39253997802734</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G502" t="n">
-        <v>9.45231056213379</v>
+        <v>9.45231151580811</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>9.34984588623047</v>
+        <v>9.34984683990479</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>11</v>
       </c>
       <c r="G505" t="n">
-        <v>9.39253902435303</v>
+        <v>9.39253997802734</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>9.09368515014648</v>
+        <v>9.09368705749512</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G507" t="n">
-        <v>9.05099487304688</v>
+        <v>9.05099391937256</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G508" t="n">
-        <v>9.04245567321777</v>
+        <v>9.04245471954346</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>9.13638019561768</v>
+        <v>9.13638114929199</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>9.13638019561768</v>
+        <v>9.13638114929199</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G511" t="n">
-        <v>9.15345764160156</v>
+        <v>9.15345668792725</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G512" t="n">
-        <v>9.22176837921143</v>
+        <v>9.22176742553711</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>9.13638019561768</v>
+        <v>9.13638114929199</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>10.75</v>
       </c>
       <c r="G514" t="n">
-        <v>9.17907333374023</v>
+        <v>9.17907524108887</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>9.09368515014648</v>
+        <v>9.09368705749512</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>10.75</v>
       </c>
       <c r="G516" t="n">
-        <v>9.17907333374023</v>
+        <v>9.17907524108887</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G517" t="n">
-        <v>9.34984588623047</v>
+        <v>9.34984683990479</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>11</v>
       </c>
       <c r="G518" t="n">
-        <v>9.39253902435303</v>
+        <v>9.39253997802734</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G521" t="n">
-        <v>9.56331348419189</v>
+        <v>9.56331443786621</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34984588623047</v>
+        <v>9.34984683990479</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G527" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870262145996</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G528" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870262145996</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870262145996</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>11.5</v>
       </c>
       <c r="G531" t="n">
-        <v>9.81947326660156</v>
+        <v>9.81947422027588</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>9.64869976043701</v>
+        <v>9.64870262145996</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G535" t="n">
-        <v>9.34984588623047</v>
+        <v>9.34984683990479</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>9.05099487304688</v>
+        <v>9.05099391937256</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G538" t="n">
-        <v>9.05099487304688</v>
+        <v>9.05099391937256</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G539" t="n">
-        <v>9.13638019561768</v>
+        <v>9.13638114929199</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>9.09368515014648</v>
+        <v>9.09368705749512</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>9.13638019561768</v>
+        <v>9.13638114929199</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>8.83752632141113</v>
+        <v>8.83752727508545</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G543" t="n">
-        <v>9.09368515014648</v>
+        <v>9.09368705749512</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>9.05099487304688</v>
+        <v>9.05099391937256</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>9.09368515014648</v>
+        <v>9.09368705749512</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>9.09368515014648</v>
+        <v>9.09368705749512</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>9.09368515014648</v>
+        <v>9.09368705749512</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>10.25</v>
       </c>
       <c r="G554" t="n">
-        <v>8.75214004516602</v>
+        <v>8.75213813781738</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>10.25</v>
       </c>
       <c r="G556" t="n">
-        <v>8.75214004516602</v>
+        <v>8.75213813781738</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>8.83752632141113</v>
+        <v>8.83752727508545</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>8.83752632141113</v>
+        <v>8.83752727508545</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>9.09368515014648</v>
+        <v>9.09368705749512</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>10.25</v>
       </c>
       <c r="G567" t="n">
-        <v>8.75214004516602</v>
+        <v>8.75213813781738</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>8.66675186157227</v>
+        <v>8.6667537689209</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>10.25</v>
       </c>
       <c r="G569" t="n">
-        <v>8.75214004516602</v>
+        <v>8.75213813781738</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>8.66675186157227</v>
+        <v>8.6667537689209</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>10</v>
       </c>
       <c r="G572" t="n">
-        <v>8.53867340087891</v>
+        <v>8.53867435455322</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G573" t="n">
-        <v>8.5215950012207</v>
+        <v>8.52159595489502</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>8.58136558532715</v>
+        <v>8.58136749267578</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G577" t="n">
-        <v>8.58136558532715</v>
+        <v>8.58136749267578</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G578" t="n">
-        <v>8.38497829437256</v>
+        <v>8.38497734069824</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>10</v>
       </c>
       <c r="G579" t="n">
-        <v>8.53867340087891</v>
+        <v>8.53867435455322</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G580" t="n">
-        <v>8.58136558532715</v>
+        <v>8.58136749267578</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>10.25</v>
       </c>
       <c r="G582" t="n">
-        <v>8.75214004516602</v>
+        <v>8.75213813781738</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>8.83752632141113</v>
+        <v>8.83752727508545</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>9.13638019561768</v>
+        <v>9.13638114929199</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>9.05099487304688</v>
+        <v>9.05099391937256</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G595" t="n">
-        <v>8.88022041320801</v>
+        <v>8.88021945953369</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>8.83752632141113</v>
+        <v>8.83752727508545</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>8.83752632141113</v>
+        <v>8.83752727508545</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G599" t="n">
-        <v>9.02945613861084</v>
+        <v>9.02945709228516</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>10.25</v>
       </c>
       <c r="G600" t="n">
-        <v>8.94221591949463</v>
+        <v>8.94221496582031</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>9.02945613861084</v>
+        <v>9.02945709228516</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>9.02945613861084</v>
+        <v>9.02945709228516</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="n">
-        <v>8.94221591949463</v>
+        <v>8.94221496582031</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>10.25</v>
       </c>
       <c r="G609" t="n">
-        <v>8.94221591949463</v>
+        <v>8.94221496582031</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>10.25</v>
       </c>
       <c r="G611" t="n">
-        <v>8.94221591949463</v>
+        <v>8.94221496582031</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G615" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G618" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>8.58452701568604</v>
+        <v>8.58452606201172</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G621" t="n">
-        <v>8.65431976318359</v>
+        <v>8.65432071685791</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>8.65431976318359</v>
+        <v>8.65432071685791</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G623" t="n">
-        <v>8.61942386627197</v>
+        <v>8.61942481994629</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G624" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G627" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176723480225</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G631" t="n">
-        <v>8.37514972686768</v>
+        <v>8.37514781951904</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G632" t="n">
-        <v>8.2006664276123</v>
+        <v>8.20066547393799</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>8.25300979614258</v>
+        <v>8.25301265716553</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G637" t="n">
-        <v>8.70666408538818</v>
+        <v>8.7066650390625</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G638" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G639" t="n">
-        <v>8.5670804977417</v>
+        <v>8.56707954406738</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G640" t="n">
-        <v>8.61942386627197</v>
+        <v>8.61942481994629</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G642" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="n">
-        <v>8.70666408538818</v>
+        <v>8.7066650390625</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G644" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G649" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176723480225</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G650" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G654" t="n">
-        <v>8.70666408538818</v>
+        <v>8.7066650390625</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G655" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176723480225</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G656" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176723480225</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G657" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>8.58452701568604</v>
+        <v>8.58452606201172</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>8.61942386627197</v>
+        <v>8.61942481994629</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G660" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>8.58452701568604</v>
+        <v>8.58452606201172</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G662" t="n">
-        <v>8.70666408538818</v>
+        <v>8.7066650390625</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>10.25</v>
       </c>
       <c r="G666" t="n">
-        <v>8.94221591949463</v>
+        <v>8.94221496582031</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G672" t="n">
-        <v>8.70666408538818</v>
+        <v>8.7066650390625</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G676" t="n">
-        <v>8.601975440979</v>
+        <v>8.60197639465332</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G677" t="n">
-        <v>8.61942386627197</v>
+        <v>8.61942481994629</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G680" t="n">
-        <v>8.65431976318359</v>
+        <v>8.65432071685791</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G681" t="n">
-        <v>8.5670804977417</v>
+        <v>8.56707954406738</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G682" t="n">
-        <v>8.67176818847656</v>
+        <v>8.67176723480225</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G686" t="n">
-        <v>8.70666408538818</v>
+        <v>8.7066650390625</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G687" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G688" t="n">
-        <v>8.61942386627197</v>
+        <v>8.61942481994629</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G693" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>8.65431976318359</v>
+        <v>8.65432071685791</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>9.29117870330811</v>
+        <v>9.29118061065674</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>9.11669826507568</v>
+        <v>9.11669731140137</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>10.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.94221591949463</v>
+        <v>8.94221496582031</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G704" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G705" t="n">
-        <v>9.07307815551758</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>9.07307815551758</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G707" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G710" t="n">
-        <v>8.601975440979</v>
+        <v>8.60197639465332</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G711" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G712" t="n">
-        <v>8.58452701568604</v>
+        <v>8.58452606201172</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G714" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G715" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G718" t="n">
-        <v>8.65431976318359</v>
+        <v>8.65432071685791</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G720" t="n">
-        <v>8.70666408538818</v>
+        <v>8.7066650390625</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G723" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G730" t="n">
-        <v>8.601975440979</v>
+        <v>8.60197639465332</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G731" t="n">
-        <v>8.61942386627197</v>
+        <v>8.61942481994629</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G734" t="n">
-        <v>8.39259624481201</v>
+        <v>8.39259719848633</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G738" t="n">
-        <v>8.37514972686768</v>
+        <v>8.37514781951904</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G740" t="n">
-        <v>8.27045917510986</v>
+        <v>8.27045822143555</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>8.25300979614258</v>
+        <v>8.25301265716553</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G745" t="n">
-        <v>8.27045917510986</v>
+        <v>8.27045822143555</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G746" t="n">
-        <v>8.06107997894287</v>
+        <v>8.06107902526855</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G748" t="n">
-        <v>8.27045917510986</v>
+        <v>8.27045822143555</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G749" t="n">
-        <v>8.11342525482178</v>
+        <v>8.11342430114746</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G750" t="n">
-        <v>8.09597682952881</v>
+        <v>8.09597778320312</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G751" t="n">
-        <v>8.2006664276123</v>
+        <v>8.20066547393799</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G752" t="n">
-        <v>8.2006664276123</v>
+        <v>8.20066547393799</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.11342525482178</v>
+        <v>8.11342430114746</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G754" t="n">
-        <v>8.1483211517334</v>
+        <v>8.14832210540771</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G756" t="n">
-        <v>8.2006664276123</v>
+        <v>8.20066547393799</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G757" t="n">
-        <v>8.11342525482178</v>
+        <v>8.11342430114746</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>8.11342525482178</v>
+        <v>8.11342430114746</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G759" t="n">
-        <v>8.2006664276123</v>
+        <v>8.20066547393799</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G760" t="n">
-        <v>8.06107997894287</v>
+        <v>8.06107902526855</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G761" t="n">
-        <v>8.1483211517334</v>
+        <v>8.14832210540771</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G763" t="n">
-        <v>8.18321895599365</v>
+        <v>8.18321704864502</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G764" t="n">
-        <v>8.11342525482178</v>
+        <v>8.11342430114746</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G765" t="n">
-        <v>8.11342525482178</v>
+        <v>8.11342430114746</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G766" t="n">
-        <v>8.11342525482178</v>
+        <v>8.11342430114746</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G767" t="n">
-        <v>8.11342525482178</v>
+        <v>8.11342430114746</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G768" t="n">
-        <v>8.11342525482178</v>
+        <v>8.11342430114746</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G770" t="n">
-        <v>8.44494152069092</v>
+        <v>8.4449405670166</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G771" t="n">
-        <v>8.61942386627197</v>
+        <v>8.61942481994629</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G773" t="n">
-        <v>8.63687133789062</v>
+        <v>8.63687038421631</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G774" t="n">
-        <v>8.70666408538818</v>
+        <v>8.7066650390625</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G775" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>8.81135559082031</v>
+        <v>8.81135368347168</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G786" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G787" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G789" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>9.07307815551758</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G796" t="n">
-        <v>9.20393943786621</v>
+        <v>9.20394039154053</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>9.11669826507568</v>
+        <v>9.11669731140137</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G798" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>8.76773262023926</v>
+        <v>8.76773357391357</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>10.25</v>
       </c>
       <c r="G802" t="n">
-        <v>8.94221591949463</v>
+        <v>8.94221496582031</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>8.85497379302979</v>
+        <v>8.8549747467041</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G806" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>9.07307815551758</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>9.07307815551758</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>8.98583602905273</v>
+        <v>8.98583507537842</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>9.07307815551758</v>
+        <v>9.07307720184326</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>9.55290222167969</v>
+        <v>9.552903175354</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G819" t="n">
-        <v>9.55290222167969</v>
+        <v>9.552903175354</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5</v>
       </c>
       <c r="G821" t="n">
-        <v>10.0327291488647</v>
+        <v>10.0327301025391</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>10.0763511657715</v>
+        <v>10.0763502120972</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>11.5</v>
       </c>
       <c r="G823" t="n">
-        <v>10.0327291488647</v>
+        <v>10.0327301025391</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>10.163592338562</v>
+        <v>10.1635913848877</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>10.163592338562</v>
+        <v>10.1635913848877</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>10.3380737304688</v>
+        <v>10.3380746841431</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>10.163592338562</v>
+        <v>10.1635913848877</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G842" t="n">
-        <v>9.98910999298096</v>
+        <v>9.98910808563232</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>11.5</v>
       </c>
       <c r="G843" t="n">
-        <v>10.0327291488647</v>
+        <v>10.0327301025391</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>11.5</v>
       </c>
       <c r="G844" t="n">
-        <v>10.0327291488647</v>
+        <v>10.0327301025391</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>9.98910999298096</v>
+        <v>9.98910808563232</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>10.5589723587036</v>
+        <v>10.5589733123779</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>10.6035251617432</v>
+        <v>10.6035242080688</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="n">
-        <v>10.5144214630127</v>
+        <v>10.5144195556641</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>10.5144214630127</v>
+        <v>10.5144195556641</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>10.5589723587036</v>
+        <v>10.5589733123779</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G855" t="n">
-        <v>10.2916574478149</v>
+        <v>10.2916564941406</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="n">
-        <v>10.1579990386963</v>
+        <v>10.157998085022</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>10.4253149032593</v>
+        <v>10.4253158569336</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>10.4253149032593</v>
+        <v>10.4253158569336</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>10.5144214630127</v>
+        <v>10.5144195556641</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>11.5</v>
       </c>
       <c r="G871" t="n">
-        <v>10.2471036911011</v>
+        <v>10.2471046447754</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>11.5</v>
       </c>
       <c r="G872" t="n">
-        <v>10.2471036911011</v>
+        <v>10.2471046447754</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>11.5</v>
       </c>
       <c r="G873" t="n">
-        <v>10.2471036911011</v>
+        <v>10.2471046447754</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>11.5</v>
       </c>
       <c r="G874" t="n">
-        <v>10.2471036911011</v>
+        <v>10.2471046447754</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>10.2025527954102</v>
+        <v>10.2025508880615</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G876" t="n">
-        <v>10.2025527954102</v>
+        <v>10.2025508880615</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134452819824</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>11.5</v>
       </c>
       <c r="G878" t="n">
-        <v>10.2471036911011</v>
+        <v>10.2471046447754</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>10.1579990386963</v>
+        <v>10.157998085022</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G880" t="n">
-        <v>10.2025527954102</v>
+        <v>10.2025508880615</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>10.2025527954102</v>
+        <v>10.2025508880615</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>10.2025527954102</v>
+        <v>10.2025508880615</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>10.1579990386963</v>
+        <v>10.157998085022</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G885" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>11.25</v>
       </c>
       <c r="G886" t="n">
-        <v>10.024341583252</v>
+        <v>10.0243425369263</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.25</v>
       </c>
       <c r="G887" t="n">
-        <v>10.024341583252</v>
+        <v>10.0243425369263</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134452819824</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134452819824</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G890" t="n">
-        <v>10.1579990386963</v>
+        <v>10.157998085022</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134452819824</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134452819824</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G893" t="n">
-        <v>10.2025527954102</v>
+        <v>10.2025508880615</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>11.25</v>
       </c>
       <c r="G895" t="n">
-        <v>10.024341583252</v>
+        <v>10.0243425369263</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G896" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.25</v>
       </c>
       <c r="G898" t="n">
-        <v>10.024341583252</v>
+        <v>10.0243425369263</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>11</v>
       </c>
       <c r="G902" t="n">
-        <v>9.8015775680542</v>
+        <v>9.80157852172852</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11</v>
       </c>
       <c r="G905" t="n">
-        <v>9.8015775680542</v>
+        <v>9.80157852172852</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G907" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.25</v>
       </c>
       <c r="G908" t="n">
-        <v>10.024341583252</v>
+        <v>10.0243425369263</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>10.0688953399658</v>
+        <v>10.0688943862915</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>10.1579990386963</v>
+        <v>10.157998085022</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>10.1579990386963</v>
+        <v>10.157998085022</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G912" t="n">
-        <v>10.1579990386963</v>
+        <v>10.157998085022</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>10.1134462356567</v>
+        <v>10.1134452819824</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>11.25</v>
       </c>
       <c r="G914" t="n">
-        <v>10.024341583252</v>
+        <v>10.0243425369263</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>11.25</v>
       </c>
       <c r="G915" t="n">
-        <v>10.024341583252</v>
+        <v>10.0243425369263</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>11.25</v>
       </c>
       <c r="G917" t="n">
-        <v>10.024341583252</v>
+        <v>10.0243425369263</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G918" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>11.25</v>
       </c>
       <c r="G919" t="n">
-        <v>10.024341583252</v>
+        <v>10.0243425369263</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>9.93523406982422</v>
+        <v>9.93523597717285</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>9.93523406982422</v>
+        <v>9.93523597717285</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>11</v>
       </c>
       <c r="G924" t="n">
-        <v>9.8015775680542</v>
+        <v>9.80157852172852</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>9.22239398956299</v>
+        <v>9.2223949432373</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>9.31149864196777</v>
+        <v>9.31149959564209</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G929" t="n">
-        <v>9.40060520172119</v>
+        <v>9.40060615539551</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G931" t="n">
-        <v>9.53426170349121</v>
+        <v>9.53426361083984</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G933" t="n">
-        <v>9.53426170349121</v>
+        <v>9.53426361083984</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>9.40060520172119</v>
+        <v>9.40060615539551</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G935" t="n">
-        <v>9.40060520172119</v>
+        <v>9.40060615539551</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G936" t="n">
-        <v>9.40060520172119</v>
+        <v>9.40060615539551</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>9.31149864196777</v>
+        <v>9.31149959564209</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>9.04418277740479</v>
+        <v>9.04418468475342</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>9.04418277740479</v>
+        <v>9.04418468475342</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>9.04418277740479</v>
+        <v>9.04418468475342</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>9.04418277740479</v>
+        <v>9.04418468475342</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>8.99963092803955</v>
+        <v>8.99963283538818</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>9.22239398956299</v>
+        <v>9.2223949432373</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>9.31149864196777</v>
+        <v>9.31149959564209</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G960" t="n">
-        <v>9.17784214019775</v>
+        <v>9.17784118652344</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>9.04418277740479</v>
+        <v>9.04418468475342</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G962" t="n">
-        <v>9.22239398956299</v>
+        <v>9.2223949432373</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G964" t="n">
-        <v>9.04418277740479</v>
+        <v>9.04418468475342</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>8.99963092803955</v>
+        <v>8.99963283538818</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>9.04418277740479</v>
+        <v>9.04418468475342</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>8.99963092803955</v>
+        <v>8.99963283538818</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>8.99963092803955</v>
+        <v>8.99963283538818</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>8.99963092803955</v>
+        <v>8.99963283538818</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>9.31149864196777</v>
+        <v>9.31149959564209</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>9.31149864196777</v>
+        <v>9.31149959564209</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>9.22239398956299</v>
+        <v>9.2223949432373</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G976" t="n">
-        <v>9.17784214019775</v>
+        <v>9.17784118652344</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G977" t="n">
-        <v>9.22239398956299</v>
+        <v>9.2223949432373</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>9.17784214019775</v>
+        <v>9.17784118652344</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G980" t="n">
-        <v>9.40060520172119</v>
+        <v>9.40060615539551</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G982" t="n">
-        <v>9.40060520172119</v>
+        <v>9.40060615539551</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>9.48970890045166</v>
+        <v>9.48970985412598</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>10.75</v>
       </c>
       <c r="G987" t="n">
-        <v>9.57881546020508</v>
+        <v>9.57881450653076</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G990" t="n">
-        <v>10.0688953399658</v>
+        <v>10.0688943862915</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G991" t="n">
-        <v>10.0688953399658</v>
+        <v>10.0688943862915</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G992" t="n">
-        <v>10.5144214630127</v>
+        <v>10.5144195556641</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>10.8708400726318</v>
+        <v>10.8708419799805</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>12.75</v>
       </c>
       <c r="G994" t="n">
-        <v>11.3609199523926</v>
+        <v>11.3609209060669</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>11.0490522384644</v>
+        <v>11.0490531921387</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>10.7817373275757</v>
+        <v>10.7817363739014</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>11.1827096939087</v>
+        <v>11.182710647583</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>11.3163661956787</v>
+        <v>11.3163681030273</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1004" t="n">
-        <v>11.450026512146</v>
+        <v>11.4500274658203</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>13</v>
       </c>
       <c r="G1005" t="n">
-        <v>11.5836849212646</v>
+        <v>11.5836839675903</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>13.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>12.0292110443115</v>
+        <v>12.0292091369629</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>11.7173404693604</v>
+        <v>11.7173414230347</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>11.450026512146</v>
+        <v>11.4500274658203</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>11.450026512146</v>
+        <v>11.4500274658203</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>13</v>
       </c>
       <c r="G1013" t="n">
-        <v>11.5836849212646</v>
+        <v>11.5836839675903</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1014" t="n">
-        <v>11.4945774078369</v>
+        <v>11.4945783615112</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>11.7173404693604</v>
+        <v>11.7173414230347</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>11.7173404693604</v>
+        <v>11.7173414230347</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>13</v>
       </c>
       <c r="G1018" t="n">
-        <v>11.5836849212646</v>
+        <v>11.5836839675903</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1019" t="n">
-        <v>11.7173404693604</v>
+        <v>11.7173414230347</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>13</v>
       </c>
       <c r="G1024" t="n">
-        <v>11.5836849212646</v>
+        <v>11.5836839675903</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>11.7173404693604</v>
+        <v>11.7173414230347</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>14</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4747371673584</v>
+        <v>12.4747362136841</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>14.25</v>
       </c>
       <c r="G1029" t="n">
-        <v>12.6974983215332</v>
+        <v>12.6974992752075</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.652946472168</v>
+        <v>12.6529455184937</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>12.3410797119141</v>
+        <v>12.3410787582397</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>14</v>
       </c>
       <c r="G1035" t="n">
-        <v>12.4747371673584</v>
+        <v>12.4747362136841</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>14</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.4747371673584</v>
+        <v>12.4747362136841</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.2965269088745</v>
+        <v>12.2965259552002</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1041" t="n">
-        <v>12.2965269088745</v>
+        <v>12.2965259552002</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>14</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.4747371673584</v>
+        <v>12.4747362136841</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.5192880630493</v>
+        <v>12.5192890167236</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>12.5638418197632</v>
+        <v>12.5638408660889</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.5192880630493</v>
+        <v>12.5192890167236</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.5638418197632</v>
+        <v>12.5638408660889</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>14.25</v>
       </c>
       <c r="G1050" t="n">
-        <v>12.6974983215332</v>
+        <v>12.6974992752075</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1051" t="n">
-        <v>12.652946472168</v>
+        <v>12.6529455184937</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1052" t="n">
-        <v>12.5192880630493</v>
+        <v>12.5192890167236</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>11.7173404693604</v>
+        <v>11.7173414230347</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>13</v>
       </c>
       <c r="G1057" t="n">
-        <v>11.5836849212646</v>
+        <v>11.5836839675903</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>12</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.6926317214966</v>
+        <v>10.6926307678223</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>11.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.2471036911011</v>
+        <v>10.2471046447754</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>10.75</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.57881546020508</v>
+        <v>9.57881450653076</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1064" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1066" t="n">
-        <v>8.82141971588135</v>
+        <v>8.82142066955566</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1068" t="n">
-        <v>7.91254758834839</v>
+        <v>7.91254663467407</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>7.75215816497803</v>
+        <v>7.75215721130371</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.4670205116272</v>
+        <v>7.46702003479004</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.82344055175781</v>
+        <v>7.82344102859497</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1073" t="n">
-        <v>7.89472484588623</v>
+        <v>7.89472675323486</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1075" t="n">
-        <v>8.53628444671631</v>
+        <v>8.53628253936768</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.58974742889404</v>
+        <v>8.58974838256836</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>9.04418277740479</v>
+        <v>9.04418468475342</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1079" t="n">
-        <v>9.31149864196777</v>
+        <v>9.31149959564209</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>10.25</v>
       </c>
       <c r="G1080" t="n">
-        <v>9.1332893371582</v>
+        <v>9.13328838348389</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>8.99963092803955</v>
+        <v>8.99963283538818</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>10.75</v>
       </c>
       <c r="G1093" t="n">
-        <v>9.57881546020508</v>
+        <v>9.57881450653076</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>11</v>
       </c>
       <c r="G1094" t="n">
-        <v>9.8015775680542</v>
+        <v>9.80157852172852</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1097" t="n">
-        <v>9.9797887802124</v>
+        <v>9.97978782653809</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1098" t="n">
-        <v>10.2025527954102</v>
+        <v>10.2025508880615</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>10.2916574478149</v>
+        <v>10.2916564941406</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1101" t="n">
-        <v>9.71685600280762</v>
+        <v>9.71685791015625</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>10.5</v>
       </c>
       <c r="G1103" t="n">
-        <v>9.57999992370605</v>
+        <v>9.57999897003174</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>10.5</v>
       </c>
       <c r="G1104" t="n">
-        <v>9.57999992370605</v>
+        <v>9.57999897003174</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>10.5</v>
       </c>
       <c r="G1105" t="n">
-        <v>9.57999992370605</v>
+        <v>9.57999897003174</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.76247596740723</v>
+        <v>9.76247787475586</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>10.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.57999992370605</v>
+        <v>9.57999897003174</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>11</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.036190032959</v>
+        <v>10.0361909866333</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>11</v>
       </c>
       <c r="G1112" t="n">
-        <v>10.036190032959</v>
+        <v>10.0361909866333</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>11</v>
       </c>
       <c r="G1113" t="n">
-        <v>10.036190032959</v>
+        <v>10.0361909866333</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1114" t="n">
-        <v>10.3099060058594</v>
+        <v>10.3099050521851</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>11</v>
       </c>
       <c r="G1115" t="n">
-        <v>10.036190032959</v>
+        <v>10.0361909866333</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1116" t="n">
-        <v>10.3099060058594</v>
+        <v>10.3099050521851</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>11.5</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.4923801422119</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1120" t="n">
-        <v>10.7660970687866</v>
+        <v>10.7660961151123</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1122" t="n">
-        <v>10.9029531478882</v>
+        <v>10.9029521942139</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>10.5380001068115</v>
+        <v>10.5380010604858</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1126" t="n">
-        <v>10.5380001068115</v>
+        <v>10.5380010604858</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.9029531478882</v>
+        <v>10.9029521942139</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>10.4011430740356</v>
+        <v>10.4011421203613</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>11.5</v>
       </c>
       <c r="G1131" t="n">
-        <v>10.4923801422119</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>11.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.4923801422119</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>10.4011430740356</v>
+        <v>10.4011421203613</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>10.4011430740356</v>
+        <v>10.4011421203613</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.7660970687866</v>
+        <v>10.7660961151123</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.7660970687866</v>
+        <v>10.7660961151123</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>11.0398111343384</v>
+        <v>11.0398101806641</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1141" t="n">
-        <v>11.2222871780396</v>
+        <v>11.2222862243652</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1142" t="n">
-        <v>11.2222871780396</v>
+        <v>11.2222862243652</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>12.25</v>
       </c>
       <c r="G1146" t="n">
-        <v>11.1766672134399</v>
+        <v>11.1766662597656</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.2222871780396</v>
+        <v>11.2222862243652</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.7660970687866</v>
+        <v>10.7660961151123</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1155" t="n">
-        <v>10.7660970687866</v>
+        <v>10.7660961151123</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>11.0398111343384</v>
+        <v>11.0398101806641</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1157" t="n">
-        <v>10.9029531478882</v>
+        <v>10.9029521942139</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.0398111343384</v>
+        <v>11.0398101806641</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>10.9029531478882</v>
+        <v>10.9029521942139</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.7660970687866</v>
+        <v>10.7660961151123</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1165" t="n">
-        <v>11.3135242462158</v>
+        <v>11.3135251998901</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>11.3135242462158</v>
+        <v>11.3135251998901</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1167" t="n">
-        <v>11.3591432571411</v>
+        <v>11.3591423034668</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1169" t="n">
-        <v>11.131046295166</v>
+        <v>11.1310472488403</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1172" t="n">
-        <v>11.131046295166</v>
+        <v>11.1310472488403</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.2222871780396</v>
+        <v>11.2222862243652</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>12.25</v>
       </c>
       <c r="G1175" t="n">
-        <v>11.1766672134399</v>
+        <v>11.1766662597656</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1177" t="n">
-        <v>11.0398111343384</v>
+        <v>11.0398101806641</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>11.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.4923801422119</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1182" t="n">
-        <v>10.7660970687866</v>
+        <v>10.7660961151123</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>10.7660970687866</v>
+        <v>10.7660961151123</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>11.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>10.4923801422119</v>
+        <v>10.4923810958862</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1189" t="n">
-        <v>10.9029531478882</v>
+        <v>10.9029521942139</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1191" t="n">
-        <v>11.0398111343384</v>
+        <v>11.0398101806641</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1192" t="n">
-        <v>10.9029531478882</v>
+        <v>10.9029521942139</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>12.25</v>
       </c>
       <c r="G1197" t="n">
-        <v>11.1766672134399</v>
+        <v>11.1766662597656</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1198" t="n">
-        <v>11.0398111343384</v>
+        <v>11.0398101806641</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1199" t="n">
-        <v>11.2679052352905</v>
+        <v>11.2679071426392</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1200" t="n">
-        <v>11.2222871780396</v>
+        <v>11.2222862243652</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>11.4960012435913</v>
+        <v>11.496000289917</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.0398111343384</v>
+        <v>11.0398101806641</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>11.131046295166</v>
+        <v>11.1310472488403</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>11.5872373580933</v>
+        <v>11.5872383117676</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>11.5872373580933</v>
+        <v>11.5872383117676</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>11.3135242462158</v>
+        <v>11.3135251998901</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>13</v>
       </c>
       <c r="G1208" t="n">
-        <v>11.860954284668</v>
+        <v>11.8609523773193</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1209" t="n">
-        <v>11.6784772872925</v>
+        <v>11.6784782409668</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>11.9978094100952</v>
+        <v>11.9978103637695</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>11.7240962982178</v>
+        <v>11.7240972518921</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13</v>
       </c>
       <c r="G1215" t="n">
-        <v>11.860954284668</v>
+        <v>11.8609523773193</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>11.7697134017944</v>
+        <v>11.7697143554688</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>11.8153343200684</v>
+        <v>11.815333366394</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>11.5872373580933</v>
+        <v>11.5872383117676</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>11.7697134017944</v>
+        <v>11.7697143554688</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>11.6784772872925</v>
+        <v>11.6784782409668</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1221" t="n">
-        <v>11.7697134017944</v>
+        <v>11.7697143554688</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>11.7697134017944</v>
+        <v>11.7697143554688</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.7240962982178</v>
+        <v>11.7240972518921</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>13</v>
       </c>
       <c r="G1226" t="n">
-        <v>11.860954284668</v>
+        <v>11.8609523773193</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1227" t="n">
-        <v>11.8153343200684</v>
+        <v>11.815333366394</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1230" t="n">
-        <v>11.5872373580933</v>
+        <v>11.5872383117676</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.4960012435913</v>
+        <v>11.496000289917</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.6784772872925</v>
+        <v>11.6784782409668</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.7697134017944</v>
+        <v>11.7697143554688</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>11.4960012435913</v>
+        <v>11.496000289917</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1235" t="n">
-        <v>12.0434274673462</v>
+        <v>12.0434293746948</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1236" t="n">
-        <v>12.5908584594727</v>
+        <v>12.5908575057983</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>12.6820945739746</v>
+        <v>12.6820955276489</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.9558095932007</v>
+        <v>12.955810546875</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>12.8189525604248</v>
+        <v>12.8189535140991</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.0926685333252</v>
+        <v>13.0926675796509</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1243" t="n">
-        <v>13.0926685333252</v>
+        <v>13.0926675796509</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>14.25</v>
       </c>
       <c r="G1244" t="n">
-        <v>13.0014276504517</v>
+        <v>13.001428604126</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1245" t="n">
-        <v>13.0470476150513</v>
+        <v>13.0470485687256</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>12.8645725250244</v>
+        <v>12.8645706176758</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1250" t="n">
-        <v>13.0470476150513</v>
+        <v>13.0470485687256</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>13.3207626342773</v>
+        <v>13.3207635879517</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>13.3207626342773</v>
+        <v>13.3207635879517</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>13.0926685333252</v>
+        <v>13.0926675796509</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1255" t="n">
-        <v>13.0470476150513</v>
+        <v>13.0470485687256</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1256" t="n">
-        <v>12.8645725250244</v>
+        <v>12.8645706176758</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1257" t="n">
-        <v>12.6820945739746</v>
+        <v>12.6820955276489</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1258" t="n">
-        <v>12.5908584594727</v>
+        <v>12.5908575057983</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>12.8645725250244</v>
+        <v>12.8645706176758</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1261" t="n">
-        <v>12.8189525604248</v>
+        <v>12.8189535140991</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1265" t="n">
-        <v>12.4083824157715</v>
+        <v>12.4083814620972</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1266" t="n">
-        <v>12.2715244293213</v>
+        <v>12.2715253829956</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1267" t="n">
-        <v>12.2715244293213</v>
+        <v>12.2715253829956</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>12.5908584594727</v>
+        <v>12.5908575057983</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>12.5908584594727</v>
+        <v>12.5908575057983</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1270" t="n">
-        <v>12.7277135848999</v>
+        <v>12.7277145385742</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1271" t="n">
-        <v>12.6820945739746</v>
+        <v>12.6820955276489</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1273" t="n">
-        <v>12.7277135848999</v>
+        <v>12.7277145385742</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>13.0926685333252</v>
+        <v>13.0926675796509</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1276" t="n">
-        <v>12.9558095932007</v>
+        <v>12.955810546875</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>12.9558095932007</v>
+        <v>12.955810546875</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1279" t="n">
-        <v>12.9558095932007</v>
+        <v>12.955810546875</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1280" t="n">
-        <v>12.9558095932007</v>
+        <v>12.955810546875</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>12.6820945739746</v>
+        <v>12.6820955276489</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>12.6364784240723</v>
+        <v>12.6364774703979</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1284" t="n">
-        <v>12.4083824157715</v>
+        <v>12.4083814620972</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>12.4083824157715</v>
+        <v>12.4083814620972</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>13.75</v>
       </c>
       <c r="G1286" t="n">
-        <v>12.5452375411987</v>
+        <v>12.5452394485474</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1287" t="n">
-        <v>12.8189525604248</v>
+        <v>12.8189535140991</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1290" t="n">
-        <v>12.8189525604248</v>
+        <v>12.8189535140991</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1291" t="n">
-        <v>12.7277135848999</v>
+        <v>12.7277145385742</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1292" t="n">
-        <v>12.9558095932007</v>
+        <v>12.955810546875</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1293" t="n">
-        <v>13.0470476150513</v>
+        <v>13.0470485687256</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>14.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>13.2295255661011</v>
+        <v>13.2295246124268</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1297" t="n">
-        <v>13.8225717544556</v>
+        <v>13.8225727081299</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>14.0506677627563</v>
+        <v>14.050666809082</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1300" t="n">
-        <v>14.0050487518311</v>
+        <v>14.0050477981567</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.5524759292603</v>
+        <v>14.5524778366089</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1309" t="n">
-        <v>14.9174289703369</v>
+        <v>14.9174299240112</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>15.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>14.1419048309326</v>
+        <v>14.1419057846069</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>15.5</v>
       </c>
       <c r="G1318" t="n">
-        <v>14.1419048309326</v>
+        <v>14.1419057846069</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1320" t="n">
-        <v>13.8681917190552</v>
+        <v>13.8681898117065</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1322" t="n">
-        <v>14.0050487518311</v>
+        <v>14.0050477981567</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>14.0050487518311</v>
+        <v>14.0050477981567</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>13.5488586425781</v>
+        <v>13.5488576889038</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1326" t="n">
-        <v>13.5488586425781</v>
+        <v>13.5488576889038</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1329" t="n">
-        <v>13.0926685333252</v>
+        <v>13.0926675796509</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>15</v>
       </c>
       <c r="G1330" t="n">
-        <v>13.6857147216797</v>
+        <v>13.6857137680054</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>14.0506677627563</v>
+        <v>14.050666809082</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>14.75</v>
       </c>
       <c r="G1332" t="n">
-        <v>13.4576187133789</v>
+        <v>13.4576196670532</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>15</v>
       </c>
       <c r="G1334" t="n">
-        <v>13.6857147216797</v>
+        <v>13.6857137680054</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>15</v>
       </c>
       <c r="G1337" t="n">
-        <v>13.6857147216797</v>
+        <v>13.6857137680054</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1340" t="n">
-        <v>14.5524759292603</v>
+        <v>14.5524778366089</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>16.25</v>
       </c>
       <c r="G1341" t="n">
-        <v>14.826189994812</v>
+        <v>14.8261919021606</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>14.9174289703369</v>
+        <v>14.9174299240112</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1345" t="n">
-        <v>14.0506677627563</v>
+        <v>14.050666809082</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>15.5</v>
       </c>
       <c r="G1348" t="n">
-        <v>14.1419048309326</v>
+        <v>14.1419057846069</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1349" t="n">
-        <v>13.8225717544556</v>
+        <v>13.8225727081299</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>14.0050487518311</v>
+        <v>14.0050477981567</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.8681917190552</v>
+        <v>13.8681898117065</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1352" t="n">
-        <v>13.8225717544556</v>
+        <v>13.8225727081299</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>15.25</v>
       </c>
       <c r="G1353" t="n">
-        <v>13.9138088226318</v>
+        <v>13.9138097763062</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1355" t="n">
-        <v>14.2574758529663</v>
+        <v>14.257474899292</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1356" t="n">
-        <v>14.3503580093384</v>
+        <v>14.3503570556641</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="n">
-        <v>14.768328666687</v>
+        <v>14.7683296203613</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1363" t="n">
-        <v>14.8147706985474</v>
+        <v>14.8147716522217</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1364" t="n">
-        <v>15.0469779968262</v>
+        <v>15.0469789505005</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1366" t="n">
-        <v>14.768328666687</v>
+        <v>14.7683296203613</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>16</v>
       </c>
       <c r="G1367" t="n">
-        <v>14.8612127304077</v>
+        <v>14.8612117767334</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1372" t="n">
-        <v>14.8147706985474</v>
+        <v>14.8147716522217</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>15.1863012313843</v>
+        <v>15.1863021850586</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>16</v>
       </c>
       <c r="G1375" t="n">
-        <v>14.8612127304077</v>
+        <v>14.8612117767334</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1376" t="n">
-        <v>15.0469779968262</v>
+        <v>15.0469789505005</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1378" t="n">
-        <v>14.768328666687</v>
+        <v>14.7683296203613</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>16</v>
       </c>
       <c r="G1379" t="n">
-        <v>14.8612127304077</v>
+        <v>14.8612117767334</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>16.25</v>
       </c>
       <c r="G1384" t="n">
-        <v>15.0934181213379</v>
+        <v>15.0934190750122</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1385" t="n">
-        <v>15.3720645904541</v>
+        <v>15.3720664978027</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>16.75</v>
       </c>
       <c r="G1387" t="n">
-        <v>15.5578317642212</v>
+        <v>15.5578298568726</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1388" t="n">
-        <v>15.6042728424072</v>
+        <v>15.6042718887329</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>17</v>
       </c>
       <c r="G1390" t="n">
-        <v>15.7900390625</v>
+        <v>15.7900371551514</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>17</v>
       </c>
       <c r="G1391" t="n">
-        <v>15.7900390625</v>
+        <v>15.7900371551514</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1392" t="n">
-        <v>15.6507158279419</v>
+        <v>15.6507139205933</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>17</v>
       </c>
       <c r="G1393" t="n">
-        <v>15.7900390625</v>
+        <v>15.7900371551514</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>17</v>
       </c>
       <c r="G1396" t="n">
-        <v>15.7900390625</v>
+        <v>15.7900371551514</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1397" t="n">
-        <v>15.6971530914307</v>
+        <v>15.697154045105</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1399" t="n">
-        <v>16.3937740325928</v>
+        <v>16.3937759399414</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.0686855316162</v>
+        <v>16.0686836242676</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1405" t="n">
-        <v>17.1368350982666</v>
+        <v>17.1368370056152</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>19</v>
       </c>
       <c r="G1406" t="n">
-        <v>17.6476879119873</v>
+        <v>17.6476898193359</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1412" t="n">
-        <v>17.1368350982666</v>
+        <v>17.1368370056152</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>19</v>
       </c>
       <c r="G1414" t="n">
-        <v>17.6476879119873</v>
+        <v>17.6476898193359</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>19.25</v>
       </c>
       <c r="G1417" t="n">
-        <v>17.8798961639404</v>
+        <v>17.8798942565918</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>20</v>
       </c>
       <c r="G1420" t="n">
-        <v>18.5765132904053</v>
+        <v>18.5765151977539</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>19.6911087036133</v>
+        <v>19.6911067962646</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>20.1555194854736</v>
+        <v>20.155517578125</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1435" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>21.6416397094727</v>
+        <v>21.641637802124</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>23.5</v>
       </c>
       <c r="G1449" t="n">
-        <v>21.8274040222168</v>
+        <v>21.8274059295654</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>23.5</v>
       </c>
       <c r="G1450" t="n">
-        <v>21.8274040222168</v>
+        <v>21.8274059295654</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1452" t="n">
-        <v>22.1060543060303</v>
+        <v>22.1060523986816</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>24</v>
       </c>
       <c r="G1453" t="n">
-        <v>22.291820526123</v>
+        <v>22.2918186187744</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>23</v>
       </c>
       <c r="G1455" t="n">
-        <v>21.3629932403564</v>
+        <v>21.3629913330078</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>23</v>
       </c>
       <c r="G1456" t="n">
-        <v>21.3629932403564</v>
+        <v>21.3629913330078</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>24</v>
       </c>
       <c r="G1457" t="n">
-        <v>22.291820526123</v>
+        <v>22.2918186187744</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>22.1060543060303</v>
+        <v>22.1060523986816</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>23</v>
       </c>
       <c r="G1459" t="n">
-        <v>21.3629932403564</v>
+        <v>21.3629913330078</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>20.1555194854736</v>
+        <v>20.155517578125</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>20.1555194854736</v>
+        <v>20.155517578125</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>18.1585445404053</v>
+        <v>18.1585426330566</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1469" t="n">
-        <v>20.1555194854736</v>
+        <v>20.155517578125</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.6911087036133</v>
+        <v>19.6911067962646</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1471" t="n">
-        <v>20.1555194854736</v>
+        <v>20.155517578125</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>23</v>
       </c>
       <c r="G1472" t="n">
-        <v>21.3629932403564</v>
+        <v>21.3629913330078</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>23</v>
       </c>
       <c r="G1473" t="n">
-        <v>21.3629932403564</v>
+        <v>21.3629913330078</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1475" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1478" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1479" t="n">
-        <v>22.5704669952393</v>
+        <v>22.5704650878906</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>22.5704669952393</v>
+        <v>22.5704650878906</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>24</v>
       </c>
       <c r="G1482" t="n">
-        <v>22.291820526123</v>
+        <v>22.2918186187744</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1484" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>23</v>
       </c>
       <c r="G1490" t="n">
-        <v>21.3629932403564</v>
+        <v>21.3629913330078</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>23</v>
       </c>
       <c r="G1491" t="n">
-        <v>21.3629932403564</v>
+        <v>21.3629913330078</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>23</v>
       </c>
       <c r="G1493" t="n">
-        <v>21.3629932403564</v>
+        <v>21.3629913330078</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1501" t="n">
-        <v>20.3412837982178</v>
+        <v>20.3412818908691</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>20.1555194854736</v>
+        <v>20.155517578125</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>19.8768711090088</v>
+        <v>19.8768730163574</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1505" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1508" t="n">
-        <v>20.3412837982178</v>
+        <v>20.3412818908691</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>23.5</v>
       </c>
       <c r="G1510" t="n">
-        <v>21.8274040222168</v>
+        <v>21.8274059295654</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.5487575531006</v>
+        <v>21.5487594604492</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>23.5</v>
       </c>
       <c r="G1514" t="n">
-        <v>21.8274040222168</v>
+        <v>21.8274059295654</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1518" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>24</v>
       </c>
       <c r="G1526" t="n">
-        <v>22.291820526123</v>
+        <v>22.2918186187744</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>20.3412837982178</v>
+        <v>20.3412818908691</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>19.8768711090088</v>
+        <v>19.8768730163574</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>19.7839870452881</v>
+        <v>19.7839889526367</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1538" t="n">
-        <v>21.0843448638916</v>
+        <v>21.084342956543</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1539" t="n">
-        <v>20.3412837982178</v>
+        <v>20.3412818908691</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1540" t="n">
-        <v>20.3412837982178</v>
+        <v>20.3412818908691</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.1555194854736</v>
+        <v>20.155517578125</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1546" t="n">
-        <v>20.3412837982178</v>
+        <v>20.3412818908691</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1547" t="n">
-        <v>20.7128124237061</v>
+        <v>20.7128143310547</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1554" t="n">
-        <v>19.6911087036133</v>
+        <v>19.6911067962646</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1556" t="n">
-        <v>19.6911087036133</v>
+        <v>19.6911067962646</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1558" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>19.3195743560791</v>
+        <v>19.3195762634277</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1565" t="n">
-        <v>18.669397354126</v>
+        <v>18.6693992614746</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1566" t="n">
-        <v>19.6911087036133</v>
+        <v>19.6911067962646</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1569" t="n">
-        <v>18.669397354126</v>
+        <v>18.6693992614746</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>15.6042728424072</v>
+        <v>15.6042718887329</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1573" t="n">
-        <v>14.768328666687</v>
+        <v>14.7683296203613</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1578" t="n">
-        <v>16.81174659729</v>
+        <v>16.8117485046387</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1582" t="n">
-        <v>17.6012496948242</v>
+        <v>17.6012477874756</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>19</v>
       </c>
       <c r="G1583" t="n">
-        <v>17.6476879119873</v>
+        <v>17.6476898193359</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1588" t="n">
-        <v>17.7870121002197</v>
+        <v>17.7870140075684</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1595" t="n">
-        <v>18.0563716888428</v>
+        <v>18.0563735961914</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1598" t="n">
-        <v>17.7963027954102</v>
+        <v>17.7963008880615</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1599" t="n">
-        <v>17.9634914398193</v>
+        <v>17.9634895324707</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>20</v>
       </c>
       <c r="G1600" t="n">
-        <v>18.5765132904053</v>
+        <v>18.5765151977539</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>20.25</v>
       </c>
       <c r="G1601" t="n">
-        <v>18.808723449707</v>
+        <v>18.8087215423584</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1603" t="n">
-        <v>19.7839870452881</v>
+        <v>19.7839889526367</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>21.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.9697532653809</v>
+        <v>19.9697551727295</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>20</v>
       </c>
       <c r="G1610" t="n">
-        <v>18.5765132904053</v>
+        <v>18.5765151977539</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1615" t="n">
-        <v>16.7407703399658</v>
+        <v>16.7407722473145</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1616" t="n">
-        <v>17.6118965148926</v>
+        <v>17.6118984222412</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1617" t="n">
-        <v>17.6118965148926</v>
+        <v>17.6118984222412</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1619" t="n">
-        <v>18.7670841217041</v>
+        <v>18.7670860290527</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1620" t="n">
-        <v>18.2747097015381</v>
+        <v>18.2747116088867</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>20</v>
       </c>
       <c r="G1622" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>20</v>
       </c>
       <c r="G1627" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1628" t="n">
-        <v>18.7860240936279</v>
+        <v>18.7860260009766</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>21</v>
       </c>
       <c r="G1630" t="n">
-        <v>19.8843994140625</v>
+        <v>19.8844013214111</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1633" t="n">
-        <v>20.7365894317627</v>
+        <v>20.7365875244141</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1634" t="n">
-        <v>19.9790878295898</v>
+        <v>19.9790897369385</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1635" t="n">
-        <v>20.2631492614746</v>
+        <v>20.2631511688232</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>22.5</v>
       </c>
       <c r="G1638" t="n">
-        <v>21.3047142028809</v>
+        <v>21.3047161102295</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>21</v>
       </c>
       <c r="G1639" t="n">
-        <v>19.8843994140625</v>
+        <v>19.8844013214111</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>20.5</v>
       </c>
       <c r="G1640" t="n">
-        <v>19.4109630584717</v>
+        <v>19.410961151123</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>18.3694000244141</v>
+        <v>18.3693981170654</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>20</v>
       </c>
       <c r="G1644" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>20.25</v>
       </c>
       <c r="G1646" t="n">
-        <v>19.1742458343506</v>
+        <v>19.174243927002</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1648" t="n">
-        <v>18.5398368835449</v>
+        <v>18.5398349761963</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1649" t="n">
-        <v>19.2215843200684</v>
+        <v>19.221586227417</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>20</v>
       </c>
       <c r="G1650" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1654" t="n">
-        <v>18.7860240936279</v>
+        <v>18.7860260009766</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>20</v>
       </c>
       <c r="G1658" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>20</v>
       </c>
       <c r="G1659" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>20</v>
       </c>
       <c r="G1662" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1665" t="n">
-        <v>19.2215843200684</v>
+        <v>19.221586227417</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1666" t="n">
-        <v>19.7897148132324</v>
+        <v>19.7897129058838</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1668" t="n">
-        <v>19.9790878295898</v>
+        <v>19.9790897369385</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1671" t="n">
-        <v>21.6834659576416</v>
+        <v>21.683464050293</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>22.5</v>
       </c>
       <c r="G1672" t="n">
-        <v>21.3047142028809</v>
+        <v>21.3047161102295</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1673" t="n">
-        <v>21.2100257873535</v>
+        <v>21.2100276947021</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1674" t="n">
-        <v>20.9733066558838</v>
+        <v>20.9733047485352</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1681" t="n">
-        <v>21.1153373718262</v>
+        <v>21.1153392791748</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1682" t="n">
-        <v>21.1153373718262</v>
+        <v>21.1153392791748</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>22.5</v>
       </c>
       <c r="G1683" t="n">
-        <v>21.3047142028809</v>
+        <v>21.3047161102295</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1688" t="n">
-        <v>20.7365894317627</v>
+        <v>20.7365875244141</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1691" t="n">
-        <v>19.9790878295898</v>
+        <v>19.9790897369385</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>20.25</v>
       </c>
       <c r="G1692" t="n">
-        <v>19.1742458343506</v>
+        <v>19.174243927002</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1694" t="n">
-        <v>19.2215843200684</v>
+        <v>19.221586227417</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1696" t="n">
-        <v>19.6950244903564</v>
+        <v>19.6950225830078</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>21</v>
       </c>
       <c r="G1697" t="n">
-        <v>19.8843994140625</v>
+        <v>19.8844013214111</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1699" t="n">
-        <v>21.2100257873535</v>
+        <v>21.2100276947021</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>24</v>
       </c>
       <c r="G1701" t="n">
-        <v>22.7250308990479</v>
+        <v>22.7250289916992</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>23.5</v>
       </c>
       <c r="G1702" t="n">
-        <v>22.2515907287598</v>
+        <v>22.2515926361084</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1706" t="n">
-        <v>22.1569023132324</v>
+        <v>22.1569042205811</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1708" t="n">
-        <v>21.1153373718262</v>
+        <v>21.1153392791748</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1710" t="n">
-        <v>21.2100257873535</v>
+        <v>21.2100276947021</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1717" t="n">
-        <v>19.7897148132324</v>
+        <v>19.7897129058838</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1721" t="n">
-        <v>19.7897148132324</v>
+        <v>19.7897129058838</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>20.5</v>
       </c>
       <c r="G1722" t="n">
-        <v>19.4109630584717</v>
+        <v>19.410961151123</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>20</v>
       </c>
       <c r="G1723" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1724" t="n">
-        <v>18.7670841217041</v>
+        <v>18.7670860290527</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1725" t="n">
-        <v>17.895959854126</v>
+        <v>17.8959617614746</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1726" t="n">
-        <v>18.672399520874</v>
+        <v>18.6723976135254</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>20.5</v>
       </c>
       <c r="G1728" t="n">
-        <v>19.4109630584717</v>
+        <v>19.410961151123</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>20</v>
       </c>
       <c r="G1729" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>20</v>
       </c>
       <c r="G1730" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>20</v>
       </c>
       <c r="G1731" t="n">
-        <v>18.9375228881836</v>
+        <v>18.9375247955322</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1732" t="n">
-        <v>19.3162746429443</v>
+        <v>19.316276550293</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1740" t="n">
-        <v>19.7897148132324</v>
+        <v>19.7897129058838</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1742" t="n">
-        <v>20.2631492614746</v>
+        <v>20.2631511688232</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1749" t="n">
-        <v>22.4409675598145</v>
+        <v>22.4409694671631</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1751" t="n">
-        <v>23.0090942382812</v>
+        <v>23.0090923309326</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>24</v>
       </c>
       <c r="G1753" t="n">
-        <v>22.7250308990479</v>
+        <v>22.7250289916992</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>24</v>
       </c>
       <c r="G1760" t="n">
-        <v>22.7250308990479</v>
+        <v>22.7250289916992</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1770" t="n">
-        <v>24.1926860809326</v>
+        <v>24.192684173584</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1773" t="n">
-        <v>23.7192478179932</v>
+        <v>23.7192497253418</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1775" t="n">
-        <v>24.3347206115723</v>
+        <v>24.3347187042236</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1777" t="n">
-        <v>25.1395626068115</v>
+        <v>25.1395606994629</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1778" t="n">
-        <v>25.1395626068115</v>
+        <v>25.1395606994629</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1781" t="n">
-        <v>26.6545639038086</v>
+        <v>26.6545658111572</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1782" t="n">
-        <v>26.6545639038086</v>
+        <v>26.6545658111572</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1783" t="n">
-        <v>26.6545639038086</v>
+        <v>26.6545658111572</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G1784" t="n">
-        <v>26.5598793029785</v>
+        <v>26.5598773956299</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1787" t="n">
-        <v>24.1926860809326</v>
+        <v>24.192684173584</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1788" t="n">
-        <v>24.1926860809326</v>
+        <v>24.192684173584</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>26</v>
       </c>
       <c r="G1789" t="n">
-        <v>24.6187839508057</v>
+        <v>24.618782043457</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G1791" t="n">
-        <v>25.0448760986328</v>
+        <v>25.0448780059814</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1792" t="n">
-        <v>25.5183162689209</v>
+        <v>25.5183143615723</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>27</v>
       </c>
       <c r="G1793" t="n">
-        <v>25.5656585693359</v>
+        <v>25.5656604766846</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G1796" t="n">
-        <v>25.2342510223389</v>
+        <v>25.2342491149902</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>25.7076873779297</v>
+        <v>25.7076892852783</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1798" t="n">
-        <v>25.1395626068115</v>
+        <v>25.1395606994629</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1801" t="n">
-        <v>25.1395626068115</v>
+        <v>25.1395606994629</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>26</v>
       </c>
       <c r="G1802" t="n">
-        <v>24.6187839508057</v>
+        <v>24.618782043457</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1809" t="n">
-        <v>26.6545639038086</v>
+        <v>26.6545658111572</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1811" t="n">
-        <v>26.9386291503906</v>
+        <v>26.9386310577393</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>31.75</v>
       </c>
       <c r="G1813" t="n">
-        <v>30.0633201599121</v>
+        <v>30.0633220672607</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1827" t="n">
-        <v>28.9270668029785</v>
+        <v>28.9270687103271</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1828" t="n">
-        <v>28.8323822021484</v>
+        <v>28.8323802947998</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1834" t="n">
-        <v>29.0217552185059</v>
+        <v>29.0217571258545</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G1845" t="n">
-        <v>29.7792587280273</v>
+        <v>29.7792568206787</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G1847" t="n">
-        <v>30.4420738220215</v>
+        <v>30.4420719146729</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1848" t="n">
-        <v>30.0159778594971</v>
+        <v>30.0159759521484</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>31.75</v>
       </c>
       <c r="G1849" t="n">
-        <v>30.0633201599121</v>
+        <v>30.0633220672607</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1854" t="n">
-        <v>29.542537689209</v>
+        <v>29.5425395965576</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1857" t="n">
-        <v>28.9270668029785</v>
+        <v>28.9270687103271</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1859" t="n">
-        <v>28.8323822021484</v>
+        <v>28.8323802947998</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1862" t="n">
-        <v>27.9801921844482</v>
+        <v>27.9801940917969</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1863" t="n">
-        <v>28.074878692627</v>
+        <v>28.0748805999756</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1865" t="n">
-        <v>28.7850379943848</v>
+        <v>28.7850360870361</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1867" t="n">
-        <v>27.9801921844482</v>
+        <v>27.9801940917969</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>64.3000030517578</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>23447</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>65.4000015258789</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>63.4000015258789</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>65.3000030517578</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>63.2000007629395</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>63.2000007629395</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>
